--- a/roadline-geojson/当別出張所管内.xlsx
+++ b/roadline-geojson/当別出張所管内.xlsx
@@ -8,322 +8,1095 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365tsukuba-my.sharepoint.com/personal/s1911313_u_tsukuba_ac_jp/Documents/GitHub/roadline-geojson/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27397913-ACEC-6841-AC3B-BA9200FD14AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_90B20E4DBD67C52B1D832B8546A83E5428329E08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29F4631A-772A-6542-A84B-EA5DE8202A1D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{1633FA64-0117-3644-8A3F-61FE52BF3F18}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1139 江別奈井江線" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Restored" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="357">
+  <si>
+    <t>図面番号</t>
+  </si>
+  <si>
+    <t>L-座標番号</t>
+  </si>
+  <si>
+    <t>L-X座標</t>
+  </si>
+  <si>
+    <t>L-Y座標</t>
+  </si>
+  <si>
+    <t>L-幅員</t>
+  </si>
+  <si>
+    <t>L-備考</t>
+  </si>
+  <si>
+    <t>R-座標番号</t>
+  </si>
+  <si>
+    <t>R-X座標</t>
+  </si>
+  <si>
+    <t>R-Y座標</t>
+  </si>
+  <si>
+    <t>R-幅員</t>
+  </si>
+  <si>
+    <t>R-備考</t>
+  </si>
+  <si>
+    <t>51-1</t>
+  </si>
+  <si>
+    <t>L-1</t>
+  </si>
+  <si>
+    <t>R-1</t>
+  </si>
+  <si>
+    <t>L-2</t>
+  </si>
+  <si>
+    <t>L-1(51-2)座標欠損</t>
+  </si>
+  <si>
+    <t>R-2</t>
+  </si>
+  <si>
+    <t>幅員欠損</t>
+  </si>
+  <si>
+    <t>51-2</t>
+  </si>
+  <si>
+    <t>L-1座標欠損</t>
+  </si>
+  <si>
+    <t>L-3</t>
+  </si>
+  <si>
+    <t>R-3</t>
+  </si>
+  <si>
+    <t>L-4</t>
+  </si>
+  <si>
+    <t>R-4</t>
+  </si>
+  <si>
+    <t>L-5</t>
+  </si>
+  <si>
+    <t>R-5</t>
+  </si>
+  <si>
+    <t>L-6</t>
+  </si>
+  <si>
+    <t>R-6</t>
+  </si>
+  <si>
+    <t>L-7</t>
+  </si>
+  <si>
+    <t>R-7</t>
+  </si>
+  <si>
+    <t>L-8</t>
+  </si>
+  <si>
+    <t>R-8</t>
+  </si>
+  <si>
+    <t>L-9</t>
+  </si>
+  <si>
+    <t>R-9</t>
+  </si>
+  <si>
+    <t>L-10</t>
+  </si>
+  <si>
+    <t>R-10</t>
+  </si>
+  <si>
+    <t>L-11</t>
+  </si>
+  <si>
+    <t>R-11</t>
+  </si>
+  <si>
+    <t>L-12</t>
+  </si>
+  <si>
+    <t>R-12</t>
+  </si>
+  <si>
+    <t>L-13</t>
+  </si>
+  <si>
+    <t>R-13</t>
+  </si>
+  <si>
+    <t>L-14</t>
+  </si>
+  <si>
+    <t>R-14</t>
+  </si>
+  <si>
+    <t>L-15</t>
+  </si>
+  <si>
+    <t>R-15</t>
+  </si>
+  <si>
+    <t>L-16</t>
+  </si>
+  <si>
+    <t>R-16</t>
+  </si>
+  <si>
+    <t>L-17</t>
+  </si>
+  <si>
+    <t>R-17</t>
+  </si>
+  <si>
+    <t>L-18</t>
+  </si>
+  <si>
+    <t>R-18</t>
+  </si>
+  <si>
+    <t>L-19</t>
+  </si>
+  <si>
+    <t>R-19</t>
+  </si>
+  <si>
+    <t>L-20</t>
+  </si>
+  <si>
+    <t>R-20</t>
+  </si>
+  <si>
+    <t>L-21</t>
+  </si>
+  <si>
+    <t>R-21</t>
+  </si>
   <si>
     <t>L-22</t>
   </si>
   <si>
+    <t>R-22</t>
+  </si>
+  <si>
+    <t>L-23</t>
+  </si>
+  <si>
+    <t>R-23</t>
+  </si>
+  <si>
+    <t>L-24</t>
+  </si>
+  <si>
+    <t>R-24</t>
+  </si>
+  <si>
+    <t>L-25</t>
+  </si>
+  <si>
+    <t>L-26</t>
+  </si>
+  <si>
+    <t>L-27</t>
+  </si>
+  <si>
+    <t>L-28</t>
+  </si>
+  <si>
+    <t>L-29</t>
+  </si>
+  <si>
+    <t>51-3</t>
+  </si>
+  <si>
+    <t>51-4</t>
+  </si>
+  <si>
+    <t>L-I1</t>
+  </si>
+  <si>
     <t>51-5</t>
+  </si>
+  <si>
+    <t>51-6</t>
+  </si>
+  <si>
+    <t>外れ値のためR-12除外</t>
+  </si>
+  <si>
+    <t>R-25</t>
+  </si>
+  <si>
+    <t>L-30</t>
+  </si>
+  <si>
+    <t>L-31</t>
+  </si>
+  <si>
+    <t>L-32</t>
+  </si>
+  <si>
+    <t>L-33</t>
+  </si>
+  <si>
+    <t>L-34</t>
+  </si>
+  <si>
+    <t>L-35</t>
+  </si>
+  <si>
+    <t>51-7</t>
+  </si>
+  <si>
+    <t>51-8</t>
+  </si>
+  <si>
+    <t>R-12〜15の座標欠損（世界測地系の記載なし）</t>
+  </si>
+  <si>
+    <t>L-18〜22の座標欠損（世界測地系の記載なし）</t>
+  </si>
+  <si>
+    <t>51-9</t>
+  </si>
+  <si>
+    <t>L-18〜22(51-8)の座標欠損（世界測地系の記載なし）</t>
+  </si>
+  <si>
+    <t>R-12〜15(51-8)の座標欠損（世界測地系の記載なし）</t>
+  </si>
+  <si>
+    <t>番号</t>
+  </si>
+  <si>
+    <t>R-X</t>
+  </si>
+  <si>
+    <t>R-Y</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>L-X</t>
+  </si>
+  <si>
+    <t>L-Y</t>
+  </si>
+  <si>
+    <t>R-I</t>
+  </si>
+  <si>
+    <t>-92169.999</t>
+  </si>
+  <si>
+    <t>-54024.736</t>
+  </si>
+  <si>
+    <t>963L-5</t>
+  </si>
+  <si>
+    <t>L- 1</t>
+  </si>
+  <si>
+    <t>-92146.788</t>
+  </si>
+  <si>
+    <t>-53,996.226</t>
+  </si>
+  <si>
+    <t>HIR-6&amp;</t>
+  </si>
+  <si>
+    <t>166.128</t>
+  </si>
+  <si>
+    <t>-53,984.845</t>
+  </si>
+  <si>
+    <t>|I L-4 11</t>
+  </si>
+  <si>
+    <t>141.717</t>
+  </si>
+  <si>
+    <t>943.495</t>
+  </si>
+  <si>
+    <t>1/ R-5 11</t>
+  </si>
+  <si>
+    <t>161.087</t>
+  </si>
+  <si>
+    <t>933.105</t>
+  </si>
+  <si>
+    <t>II L-311</t>
+  </si>
+  <si>
+    <t>136.656</t>
+  </si>
+  <si>
+    <t>890.754</t>
+  </si>
+  <si>
+    <t>// R-411</t>
+  </si>
+  <si>
+    <t>155.766</t>
+  </si>
+  <si>
+    <t>878.424</t>
+  </si>
+  <si>
+    <t>963 L-2.11</t>
+  </si>
+  <si>
+    <t>131.585</t>
+  </si>
+  <si>
+    <t>838.023</t>
+  </si>
+  <si>
+    <t>/ R-311</t>
+  </si>
+  <si>
+    <t>153.675</t>
+  </si>
+  <si>
+    <t>856.993</t>
+  </si>
+  <si>
+    <t>HIR-II</t>
+  </si>
+  <si>
+    <t>126.514</t>
+  </si>
+  <si>
+    <t>785.283</t>
+  </si>
+  <si>
+    <t>// R-2/1</t>
+  </si>
+  <si>
+    <t>148.834</t>
+  </si>
+  <si>
+    <t>807.223</t>
+  </si>
+  <si>
+    <t>HIR-21</t>
+  </si>
+  <si>
+    <t>L- 6</t>
+  </si>
+  <si>
+    <t>128.414</t>
+  </si>
+  <si>
+    <t>785.102</t>
+  </si>
+  <si>
+    <t>146.504</t>
+  </si>
+  <si>
+    <t>783.302</t>
+  </si>
+  <si>
+    <t>963 L-111</t>
+  </si>
+  <si>
+    <t>119.282</t>
+  </si>
+  <si>
+    <t>725.962</t>
+  </si>
+  <si>
+    <t>HI L-411</t>
+  </si>
+  <si>
+    <t>143.993</t>
+  </si>
+  <si>
+    <t>757.452</t>
+  </si>
+  <si>
+    <t>HIR-311</t>
+  </si>
+  <si>
+    <t>117.262</t>
+  </si>
+  <si>
+    <t>718.272</t>
+  </si>
+  <si>
+    <t>I/ L-5 11</t>
+  </si>
+  <si>
+    <t>139.152</t>
+  </si>
+  <si>
+    <t>707.681</t>
+  </si>
+  <si>
+    <t>11 R-41</t>
+  </si>
+  <si>
+    <t>111.691</t>
+  </si>
+  <si>
+    <t>668.581</t>
+  </si>
+  <si>
+    <t>I L-611</t>
+  </si>
+  <si>
+    <t>131.200</t>
+  </si>
+  <si>
+    <t>618.680</t>
+  </si>
+  <si>
+    <t>/I R-5|1</t>
+  </si>
+  <si>
+    <t>106.370</t>
+  </si>
+  <si>
+    <t>621.110</t>
+  </si>
+  <si>
+    <t>HI L-711</t>
+  </si>
+  <si>
+    <t>142.430</t>
+  </si>
+  <si>
+    <t>617.560</t>
+  </si>
+  <si>
+    <t>/ R-6 |I</t>
+  </si>
+  <si>
+    <t>104.170</t>
+  </si>
+  <si>
+    <t>603.080</t>
+  </si>
+  <si>
+    <t>963 R-7 1|</t>
+  </si>
+  <si>
+    <t>139.830</t>
+  </si>
+  <si>
+    <t>610.460</t>
+  </si>
+  <si>
+    <t>11 R-711</t>
+  </si>
+  <si>
+    <t>099.849</t>
+  </si>
+  <si>
+    <t>567.079</t>
+  </si>
+  <si>
+    <t>| R-6 /1</t>
+  </si>
+  <si>
+    <t>135.840</t>
+  </si>
+  <si>
+    <t>599.940</t>
+  </si>
+  <si>
+    <t>/ R-811</t>
+  </si>
+  <si>
+    <t>L- 13</t>
+  </si>
+  <si>
+    <t>097.045</t>
+  </si>
+  <si>
+    <t>550.097</t>
+  </si>
+  <si>
+    <t>H23 L 13</t>
+  </si>
+  <si>
+    <t>128.650</t>
+  </si>
+  <si>
+    <t>597.200</t>
+  </si>
+  <si>
+    <t>HIR-911</t>
+  </si>
+  <si>
+    <t>090.922</t>
+  </si>
+  <si>
+    <t>511.039</t>
+  </si>
+  <si>
+    <t>" L 14</t>
+  </si>
+  <si>
+    <t>-92125.869</t>
+  </si>
+  <si>
+    <t>-53572.309</t>
+  </si>
+  <si>
+    <t>963L-11麦</t>
+  </si>
+  <si>
+    <t>- 92,089.117</t>
+  </si>
+  <si>
+    <t>- 53,499.208</t>
+  </si>
+  <si>
+    <t>H23 L 15</t>
+  </si>
+  <si>
+    <t>-92127.839</t>
+  </si>
+  <si>
+    <t>-53,566.979</t>
+  </si>
+  <si>
+    <t>963 L-10 # L- 16</t>
+  </si>
+  <si>
+    <t>- 92, 100.333</t>
+  </si>
+  <si>
+    <t>- 53,499.579</t>
+  </si>
+  <si>
+    <t>H23L13</t>
+  </si>
+  <si>
+    <t>125.598</t>
+  </si>
+  <si>
+    <t>533.169</t>
+  </si>
+  <si>
+    <t>H|R-12/L-17</t>
+  </si>
+  <si>
+    <t>094.826</t>
+  </si>
+  <si>
+    <t>444.478</t>
+  </si>
+  <si>
+    <t>123.628</t>
+  </si>
+  <si>
+    <t>503.388</t>
+  </si>
+  <si>
+    <t>963 L-9 |/</t>
+  </si>
+  <si>
+    <t>088.936</t>
+  </si>
+  <si>
+    <t>444.247</t>
+  </si>
+  <si>
+    <t>128.808</t>
+  </si>
+  <si>
+    <t>501.448</t>
+  </si>
+  <si>
+    <t>|/ L-8 11</t>
+  </si>
+  <si>
+    <t>085.656</t>
+  </si>
+  <si>
+    <t>407.113</t>
+  </si>
+  <si>
+    <t>HI5L-17 #</t>
+  </si>
+  <si>
+    <t>145.027</t>
+  </si>
+  <si>
+    <t>501.488</t>
+  </si>
+  <si>
+    <t>I L-7 /</t>
+  </si>
+  <si>
+    <t>085.705</t>
+  </si>
+  <si>
+    <t>396.346</t>
+  </si>
+  <si>
+    <t>S63R-3"</t>
+  </si>
+  <si>
+    <t>145.467</t>
+  </si>
+  <si>
+    <t>500.658</t>
+  </si>
+  <si>
+    <t>// L-6 11</t>
+  </si>
+  <si>
+    <t>082.425</t>
+  </si>
+  <si>
+    <t>372.106</t>
+  </si>
+  <si>
+    <t>HIL-16"</t>
+  </si>
+  <si>
+    <t>117.956</t>
+  </si>
+  <si>
+    <t>445.207</t>
+  </si>
+  <si>
+    <t>963 L-3 11</t>
+  </si>
+  <si>
+    <t>075.623</t>
+  </si>
+  <si>
+    <t>295.925</t>
+  </si>
+  <si>
+    <t>"L-17"</t>
+  </si>
+  <si>
+    <t>116.733</t>
+  </si>
+  <si>
+    <t>437.693</t>
+  </si>
+  <si>
+    <t>158111</t>
+  </si>
+  <si>
+    <t>070.261</t>
+  </si>
+  <si>
+    <t>233.404</t>
+  </si>
+  <si>
+    <t>"L-18"</t>
+  </si>
+  <si>
+    <t>R-26</t>
+  </si>
+  <si>
+    <t>110.575</t>
+  </si>
+  <si>
+    <t>395.027</t>
+  </si>
+  <si>
+    <t>963 L-2</t>
+  </si>
+  <si>
+    <t>065.380</t>
+  </si>
+  <si>
+    <t>178.833</t>
+  </si>
+  <si>
+    <t>"L-19"</t>
+  </si>
+  <si>
+    <t>R-27</t>
+  </si>
+  <si>
+    <t>106.435</t>
+  </si>
+  <si>
+    <t>377.846</t>
+  </si>
+  <si>
+    <t>963 L-1 11 |L-25</t>
+  </si>
+  <si>
+    <t>060.289</t>
+  </si>
+  <si>
+    <t>124.532</t>
+  </si>
+  <si>
+    <t>"L-20"</t>
+  </si>
+  <si>
+    <t>R-28</t>
+  </si>
+  <si>
+    <t>099.603</t>
+  </si>
+  <si>
+    <t>300.965</t>
+  </si>
+  <si>
+    <t>HIR-1811 L-26</t>
+  </si>
+  <si>
+    <t>053.938</t>
+  </si>
+  <si>
+    <t>057.081</t>
+  </si>
+  <si>
+    <t>"L-21",</t>
+  </si>
+  <si>
+    <t>R-29</t>
+  </si>
+  <si>
+    <t>096.713</t>
+  </si>
+  <si>
+    <t>276.905</t>
+  </si>
+  <si>
+    <t>// R-1911</t>
+  </si>
+  <si>
+    <t>- 92,052.028</t>
+  </si>
+  <si>
+    <t>- 53,039.001</t>
+  </si>
+  <si>
+    <t>HIL-22変</t>
+  </si>
+  <si>
+    <t>R-30</t>
+  </si>
+  <si>
+    <t>088.611</t>
+  </si>
+  <si>
+    <t>195.803</t>
+  </si>
+  <si>
+    <t>// R-20 |1</t>
+  </si>
+  <si>
+    <t>R-31</t>
+  </si>
+  <si>
+    <t>082.189</t>
+  </si>
+  <si>
+    <t>133.442</t>
+  </si>
+  <si>
+    <t>// R-21 11</t>
+  </si>
+  <si>
+    <t>R-32</t>
+  </si>
+  <si>
+    <t>075.018</t>
+  </si>
+  <si>
+    <t>059.492</t>
+  </si>
+  <si>
+    <t>1/ R-22 |1</t>
+  </si>
+  <si>
+    <t>R-33</t>
+  </si>
+  <si>
+    <t>078.858</t>
+  </si>
+  <si>
+    <t>054.542</t>
+  </si>
+  <si>
+    <t>1/ R-23 ||</t>
+  </si>
+  <si>
+    <t>R-34</t>
+  </si>
+  <si>
+    <t>075.248</t>
+  </si>
+  <si>
+    <t>036.642</t>
+  </si>
+  <si>
+    <t>1/ R-24 11</t>
+  </si>
+  <si>
+    <t>R-35</t>
+  </si>
+  <si>
+    <t>-92,072.508</t>
+  </si>
+  <si>
+    <t>-53,035.321</t>
+  </si>
+  <si>
+    <t>HI R-25#</t>
+  </si>
+  <si>
+    <t>番号.1</t>
+  </si>
+  <si>
+    <t>備考.1</t>
+  </si>
+  <si>
+    <t>R-X(復元)</t>
+  </si>
+  <si>
+    <t>R-Y(復元)</t>
+  </si>
+  <si>
+    <t>L-X(復元)</t>
+  </si>
+  <si>
+    <t>L-Y(復元)</t>
+  </si>
+  <si>
+    <t>L-1</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>L-21</t>
-  </si>
-  <si>
-    <t>R-20</t>
-  </si>
-  <si>
-    <t>L-20</t>
-  </si>
-  <si>
-    <t>R-19</t>
-  </si>
-  <si>
-    <t>L-19</t>
-  </si>
-  <si>
-    <t>R-18</t>
-  </si>
-  <si>
-    <t>L-18</t>
-  </si>
-  <si>
-    <t>R-17</t>
-  </si>
-  <si>
-    <t>L-17</t>
-  </si>
-  <si>
-    <t>R-16</t>
-  </si>
-  <si>
-    <t>L-16</t>
-  </si>
-  <si>
-    <t>R-15</t>
-  </si>
-  <si>
-    <t>L-15</t>
-  </si>
-  <si>
-    <t>R-14</t>
-  </si>
-  <si>
-    <t>L-14</t>
-  </si>
-  <si>
-    <t>R-13</t>
-  </si>
-  <si>
-    <t>L-13</t>
-  </si>
-  <si>
-    <t>R-12</t>
-  </si>
-  <si>
-    <t>L-12</t>
-  </si>
-  <si>
-    <t>R-11</t>
-  </si>
-  <si>
-    <t>L-11</t>
-  </si>
-  <si>
-    <t>R-10</t>
-  </si>
-  <si>
-    <t>L-10</t>
-  </si>
-  <si>
-    <t>R-9</t>
-  </si>
-  <si>
-    <t>L-9</t>
-  </si>
-  <si>
-    <t>R-8</t>
-  </si>
-  <si>
-    <t>L-8</t>
-  </si>
-  <si>
-    <t>R-7</t>
-  </si>
-  <si>
-    <t>L-7</t>
-  </si>
-  <si>
-    <t>R-6</t>
-  </si>
-  <si>
-    <t>L-6</t>
-  </si>
-  <si>
-    <t>R-5</t>
-  </si>
-  <si>
-    <t>L-5</t>
-  </si>
-  <si>
-    <t>R-4</t>
-  </si>
-  <si>
-    <t>L-4</t>
-  </si>
-  <si>
-    <t>R-3</t>
-  </si>
-  <si>
-    <t>L-3</t>
-  </si>
-  <si>
-    <t>R-2</t>
-  </si>
-  <si>
-    <t>L-2</t>
+    <t>51-10</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>R-1</t>
-  </si>
-  <si>
-    <t>L-1</t>
-  </si>
-  <si>
-    <t>L-26</t>
-  </si>
-  <si>
-    <t>51-4</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>L-25</t>
-  </si>
-  <si>
-    <t>L-24</t>
-  </si>
-  <si>
-    <t>R-23</t>
-  </si>
-  <si>
-    <t>L-23</t>
-  </si>
-  <si>
-    <t>R-22</t>
-  </si>
-  <si>
-    <t>R-21</t>
-  </si>
-  <si>
-    <t>L-I1</t>
-  </si>
-  <si>
-    <t>51-3</t>
-  </si>
-  <si>
-    <t>51-3</t>
+    <t>-53012.051</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>-92045.227</t>
+  </si>
+  <si>
+    <t>-52969.741</t>
+  </si>
+  <si>
+    <t>-92015.799</t>
+  </si>
+  <si>
+    <t>-91981.349</t>
+  </si>
+  <si>
+    <t>-52331.144</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>-92040.096</t>
+  </si>
+  <si>
+    <t>-91975.902</t>
+  </si>
+  <si>
+    <t>-52275.603</t>
+  </si>
+  <si>
+    <t>-92033.255</t>
+  </si>
+  <si>
+    <t>-52378.864</t>
+  </si>
+  <si>
+    <t>-91974.173</t>
+  </si>
+  <si>
+    <t>-52251.926</t>
+  </si>
+  <si>
+    <t>-92052.455</t>
+  </si>
+  <si>
+    <t>-52837.680</t>
+  </si>
+  <si>
+    <t>-92024.144</t>
+  </si>
+  <si>
+    <t>-52760.949</t>
+  </si>
+  <si>
+    <t>-52329.111</t>
+  </si>
+  <si>
+    <t>-91970.533</t>
+  </si>
+  <si>
+    <t>-52233.343</t>
+  </si>
+  <si>
+    <t>-92045.254</t>
+  </si>
+  <si>
+    <t>-52765.549</t>
+  </si>
+  <si>
+    <t>-92015.832</t>
+  </si>
+  <si>
+    <t>-52679.078</t>
+  </si>
+  <si>
+    <t>노로</t>
+  </si>
+  <si>
+    <t>-91964.753</t>
+  </si>
+  <si>
+    <t>-52215.519</t>
+  </si>
+  <si>
+    <t>-92039.143</t>
+  </si>
+  <si>
+    <t>-52702.418</t>
+  </si>
+  <si>
+    <t>-92008.271</t>
+  </si>
+  <si>
+    <t>-52603.547</t>
+  </si>
+  <si>
+    <t>-52194.546</t>
+  </si>
+  <si>
+    <t>-52198.555</t>
+  </si>
+  <si>
+    <t>-92034.792</t>
+  </si>
+  <si>
+    <t>-52657.508</t>
+  </si>
+  <si>
+    <t>-52548.817</t>
+  </si>
+  <si>
+    <t>-91948.562</t>
+  </si>
+  <si>
+    <t>-52183.008</t>
+  </si>
+  <si>
+    <t>-92024.941</t>
+  </si>
+  <si>
+    <t>-91997.570</t>
+  </si>
+  <si>
+    <t>-52496.266</t>
+  </si>
+  <si>
+    <t>-91916.911</t>
+  </si>
+  <si>
+    <t>-52124.438</t>
+  </si>
+  <si>
+    <t>1번로4</t>
+  </si>
+  <si>
+    <t>-91934.105</t>
+  </si>
+  <si>
+    <t>-52168.840</t>
+  </si>
+  <si>
+    <t>-52478.176</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>-52154.726</t>
+  </si>
+  <si>
+    <t>-91993.209</t>
+  </si>
+  <si>
+    <t>-91877.510</t>
+  </si>
+  <si>
+    <t>-52090.927</t>
+  </si>
+  <si>
+    <t>-91916.384</t>
+  </si>
+  <si>
+    <t>-52145.598</t>
+  </si>
+  <si>
+    <t>-92023.240</t>
+  </si>
+  <si>
+    <t>-91986.230</t>
+  </si>
+  <si>
+    <t>-52380.906</t>
+  </si>
+  <si>
+    <t>-91887.104</t>
+  </si>
+  <si>
+    <t>-52475.386</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>L-29</t>
-  </si>
-  <si>
-    <t>51-2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-28</t>
-  </si>
-  <si>
-    <t>L-27</t>
-  </si>
-  <si>
-    <t>R-24</t>
-  </si>
-  <si>
-    <t>L-1座標欠損</t>
-    <rPh sb="3" eb="7">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>幅員欠損</t>
-    <rPh sb="0" eb="2">
-      <t>フクイn</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケッソn</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-1(51-2)座標欠損</t>
-    <rPh sb="9" eb="13">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>51-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-備考</t>
-    <rPh sb="2" eb="4">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-幅員</t>
-    <rPh sb="2" eb="4">
-      <t>フクイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-Y座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-X座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R-座標番号</t>
-    <rPh sb="2" eb="6">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-備考</t>
-    <rPh sb="2" eb="4">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-幅員</t>
-    <rPh sb="2" eb="4">
-      <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-Y座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-X座標</t>
-    <rPh sb="3" eb="5">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>L-座標番号</t>
-    <rPh sb="2" eb="6">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>図面番号</t>
-    <rPh sb="0" eb="4">
-      <t>ズメn</t>
-    </rPh>
+    <t>51-11</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -334,7 +1107,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.000_ "/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,6 +1127,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -363,7 +1143,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -371,15 +1151,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -693,8 +1493,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66588345-0F0F-A242-ACD7-5426F04C1B6B}">
-  <dimension ref="A1:L105"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L274"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -707,51 +1507,51 @@
     <col min="9" max="10" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="1"/>
+    <col min="13" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="2"/>
+        <v>5</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>-96369.502999999997</v>
@@ -762,10 +1562,8 @@
       <c r="E2" s="2">
         <v>34.25</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2">
         <v>-96377.752999999997</v>
@@ -777,12 +1575,12 @@
         <v>30.45</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>-96367.442999999999</v>
@@ -794,11 +1592,10 @@
         <v>15.51</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="2"/>
+        <v>15</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="I3" s="2">
         <v>-96365.342999999993</v>
@@ -806,22 +1603,16 @@
       <c r="J3" s="2">
         <v>-57374.455000000002</v>
       </c>
-      <c r="K3" s="2"/>
       <c r="L3" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+        <v>18</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2">
         <v>-96318.543000000005</v>
@@ -829,14 +1620,13 @@
       <c r="J5" s="2">
         <v>-57368.154999999999</v>
       </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>-96275.444000000003</v>
@@ -844,13 +1634,11 @@
       <c r="D6" s="2">
         <v>-57391.355000000003</v>
       </c>
-      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>19</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I6" s="2">
         <v>-96263.644</v>
@@ -858,14 +1646,13 @@
       <c r="J6" s="2">
         <v>-57363.355000000003</v>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2">
         <v>-96252.944000000003</v>
@@ -873,11 +1660,8 @@
       <c r="D7" s="2">
         <v>-57384.754999999997</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I7" s="2">
         <v>-96257.02</v>
@@ -885,14 +1669,13 @@
       <c r="J7" s="2">
         <v>-57362.322999999997</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2">
         <v>-96212.194000000003</v>
@@ -900,11 +1683,8 @@
       <c r="D8" s="2">
         <v>-57376.353999999999</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2">
         <v>-96226.282999999996</v>
@@ -912,14 +1692,13 @@
       <c r="J8" s="2">
         <v>-57356.284</v>
       </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2">
         <v>-96178.444000000003</v>
@@ -927,11 +1706,8 @@
       <c r="D9" s="2">
         <v>-57370.103999999999</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
       <c r="H9" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
         <v>-96175.705000000002</v>
@@ -939,14 +1715,13 @@
       <c r="J9" s="2">
         <v>-57345.785000000003</v>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2">
         <v>-96172.644</v>
@@ -954,11 +1729,8 @@
       <c r="D10" s="2">
         <v>-57373.983999999997</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
       <c r="H10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I10" s="2">
         <v>-96174.914000000004</v>
@@ -966,14 +1738,13 @@
       <c r="J10" s="2">
         <v>-57344.864000000001</v>
       </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2">
         <v>-96172.447</v>
@@ -981,9 +1752,6 @@
       <c r="D11" s="2">
         <v>-57375.391000000003</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
       <c r="H11" s="1" t="s">
         <v>29</v>
       </c>
@@ -993,14 +1761,13 @@
       <c r="J11" s="2">
         <v>-57342.523999999998</v>
       </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2">
         <v>-96145.455000000002</v>
@@ -1008,11 +1775,8 @@
       <c r="D12" s="2">
         <v>-57371.569000000003</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
       <c r="H12" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I12" s="2">
         <v>-96149.433999999994</v>
@@ -1020,14 +1784,13 @@
       <c r="J12" s="2">
         <v>-57343.343999999997</v>
       </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2">
         <v>-96146.323999999993</v>
@@ -1035,11 +1798,8 @@
       <c r="D13" s="2">
         <v>-57365.453999999998</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I13" s="2">
         <v>-96138.752999999997</v>
@@ -1047,14 +1807,13 @@
       <c r="J13" s="2">
         <v>-57341.076000000001</v>
       </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2">
         <v>-96135.584000000003</v>
@@ -1062,11 +1821,8 @@
       <c r="D14" s="2">
         <v>-57363.444000000003</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I14" s="2">
         <v>-96138.877999999997</v>
@@ -1074,14 +1830,13 @@
       <c r="J14" s="2">
         <v>-57340.182000000001</v>
       </c>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2">
         <v>-96112.683999999994</v>
@@ -1089,11 +1844,8 @@
       <c r="D15" s="2">
         <v>-57359.163999999997</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I15" s="2">
         <v>-96127.120999999999</v>
@@ -1101,14 +1853,13 @@
       <c r="J15" s="2">
         <v>-57337.106</v>
       </c>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" s="1" customFormat="1">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2">
         <v>-96112.459000000003</v>
@@ -1116,11 +1867,8 @@
       <c r="D16" s="2">
         <v>-57360.766000000003</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I16" s="2">
         <v>-96084.895000000004</v>
@@ -1128,14 +1876,13 @@
       <c r="J16" s="2">
         <v>-57328.983</v>
       </c>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2">
         <v>-96095.581000000006</v>
@@ -1143,11 +1890,8 @@
       <c r="D17" s="2">
         <v>-57358.008000000002</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
       <c r="H17" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I17" s="2">
         <v>-96068.414999999994</v>
@@ -1155,14 +1899,13 @@
       <c r="J17" s="2">
         <v>-57326.144</v>
       </c>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2">
         <v>-96042.286999999997</v>
@@ -1170,11 +1913,8 @@
       <c r="D18" s="2">
         <v>-57346.55</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
       <c r="H18" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I18" s="2">
         <v>-95990.365000000005</v>
@@ -1182,14 +1922,13 @@
       <c r="J18" s="2">
         <v>-57310.502999999997</v>
       </c>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2">
         <v>-96042.345000000001</v>
@@ -1197,11 +1936,8 @@
       <c r="D19" s="2">
         <v>-57346.023999999998</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
       <c r="H19" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I19" s="2">
         <v>-95962.695000000007</v>
@@ -1209,14 +1945,13 @@
       <c r="J19" s="2">
         <v>-57302.313000000002</v>
       </c>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2">
         <v>-96027.294999999998</v>
@@ -1224,11 +1959,8 @@
       <c r="D20" s="2">
         <v>-57343.214</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
       <c r="H20" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="I20" s="2">
         <v>-95939.955000000002</v>
@@ -1236,14 +1968,13 @@
       <c r="J20" s="2">
         <v>-57290.623</v>
       </c>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2">
         <v>-95955.794999999998</v>
@@ -1251,11 +1982,8 @@
       <c r="D21" s="2">
         <v>-57329.843000000001</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
       <c r="H21" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I21" s="2">
         <v>-95920.785000000003</v>
@@ -1263,14 +1991,13 @@
       <c r="J21" s="2">
         <v>-57272.743000000002</v>
       </c>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2">
         <v>-95920.744999999995</v>
@@ -1278,11 +2005,8 @@
       <c r="D22" s="2">
         <v>-57312.192999999999</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
       <c r="H22" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I22" s="2">
         <v>-95908.595000000001</v>
@@ -1290,14 +2014,13 @@
       <c r="J22" s="2">
         <v>-57249.252999999997</v>
       </c>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2">
         <v>-95905.764999999999</v>
@@ -1305,11 +2028,8 @@
       <c r="D23" s="2">
         <v>-57293.012999999999</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
       <c r="H23" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I23" s="2">
         <v>-95902.335000000006</v>
@@ -1317,14 +2037,13 @@
       <c r="J23" s="2">
         <v>-57227.383000000002</v>
       </c>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2">
         <v>-95895.986000000004</v>
@@ -1332,11 +2051,8 @@
       <c r="D24" s="2">
         <v>-57279.652999999998</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
       <c r="H24" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="I24" s="2">
         <v>-95897.675000000003</v>
@@ -1344,14 +2060,13 @@
       <c r="J24" s="2">
         <v>-57190.883000000002</v>
       </c>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2">
         <v>-95889.576000000001</v>
@@ -1359,11 +2074,8 @@
       <c r="D25" s="2">
         <v>-57269.332999999999</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
       <c r="H25" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I25" s="2">
         <v>-95893.895000000004</v>
@@ -1371,14 +2083,13 @@
       <c r="J25" s="2">
         <v>-57191.262999999999</v>
       </c>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C26" s="2">
         <v>-95884.895999999993</v>
@@ -1386,11 +2097,8 @@
       <c r="D26" s="2">
         <v>-57256.423000000003</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I26" s="2">
         <v>-95888.865000000005</v>
@@ -1398,14 +2106,13 @@
       <c r="J26" s="2">
         <v>-57141.514000000003</v>
       </c>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C27" s="2">
         <v>-95880.106</v>
@@ -1413,11 +2120,8 @@
       <c r="D27" s="2">
         <v>-57236.593000000001</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
       <c r="H27" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I27" s="2">
         <v>-95883.835000000006</v>
@@ -1425,14 +2129,13 @@
       <c r="J27" s="2">
         <v>-57091.773999999998</v>
       </c>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>-95877.725999999995</v>
@@ -1440,11 +2143,8 @@
       <c r="D28" s="2">
         <v>-57223.673000000003</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
       <c r="H28" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" s="2">
         <v>-95878.815000000002</v>
@@ -1452,14 +2152,13 @@
       <c r="J28" s="2">
         <v>-57042.023999999998</v>
       </c>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2">
         <v>-95876.406000000003</v>
@@ -1467,19 +2166,13 @@
       <c r="D29" s="2">
         <v>-57210.832999999999</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2">
         <v>-95875.805999999997</v>
@@ -1487,19 +2180,13 @@
       <c r="D30" s="2">
         <v>-57193.093000000001</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C31" s="2">
         <v>-95870.785999999993</v>
@@ -1507,19 +2194,13 @@
       <c r="D31" s="2">
         <v>-57143.343000000001</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C32" s="2">
         <v>-95865.766000000003</v>
@@ -1527,19 +2208,13 @@
       <c r="D32" s="2">
         <v>-57093.603999999999</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2">
         <v>-95860.736000000004</v>
@@ -1547,19 +2222,13 @@
       <c r="D33" s="2">
         <v>-57043.853999999999</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="35" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C35" s="2">
         <v>-95855.714999999997</v>
@@ -1567,11 +2236,8 @@
       <c r="D35" s="2">
         <v>-56994.103999999999</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
       <c r="H35" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I35" s="2">
         <v>-95873.794999999998</v>
@@ -1579,14 +2245,13 @@
       <c r="J35" s="2">
         <v>-56992.273999999998</v>
       </c>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2">
         <v>-95850.695000000007</v>
@@ -1594,11 +2259,8 @@
       <c r="D36" s="2">
         <v>-56944.353999999999</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
       <c r="H36" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I36" s="2">
         <v>-95871.285000000003</v>
@@ -1606,14 +2268,13 @@
       <c r="J36" s="2">
         <v>-56967.413999999997</v>
       </c>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C37" s="2">
         <v>-95845.675000000003</v>
@@ -1621,11 +2282,8 @@
       <c r="D37" s="2">
         <v>-56894.603999999999</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
       <c r="H37" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I37" s="2">
         <v>-95874.264999999999</v>
@@ -1633,14 +2291,13 @@
       <c r="J37" s="2">
         <v>-56967.114000000001</v>
       </c>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C38" s="2">
         <v>-95840.654999999999</v>
@@ -1648,11 +2305,8 @@
       <c r="D38" s="2">
         <v>-56844.864000000001</v>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
       <c r="H38" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I38" s="2">
         <v>-95866.755000000005</v>
@@ -1660,14 +2314,13 @@
       <c r="J38" s="2">
         <v>-56892.694000000003</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C39" s="2">
         <v>-95835.625</v>
@@ -1675,11 +2328,8 @@
       <c r="D39" s="2">
         <v>-56795.114000000001</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
       <c r="H39" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I39" s="2">
         <v>-95861.735000000001</v>
@@ -1687,14 +2337,13 @@
       <c r="J39" s="2">
         <v>-56842.944000000003</v>
       </c>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C40" s="2">
         <v>-95830.604999999996</v>
@@ -1702,11 +2351,8 @@
       <c r="D40" s="2">
         <v>-56745.364999999998</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
       <c r="H40" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I40" s="2">
         <v>-95856.714999999997</v>
@@ -1714,14 +2360,13 @@
       <c r="J40" s="2">
         <v>-56793.194000000003</v>
       </c>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2">
         <v>-95826.138000000006</v>
@@ -1729,9 +2374,6 @@
       <c r="D41" s="2">
         <v>-56701.341</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
       <c r="H41" s="1" t="s">
         <v>29</v>
       </c>
@@ -1741,14 +2383,13 @@
       <c r="J41" s="2">
         <v>-56743.455000000002</v>
       </c>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C42" s="2">
         <v>-95825.392999999996</v>
@@ -1756,11 +2397,8 @@
       <c r="D42" s="2">
         <v>-56698.887000000002</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
       <c r="H42" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I42" s="2">
         <v>-95846.956999999995</v>
@@ -1768,14 +2406,13 @@
       <c r="J42" s="2">
         <v>-56696.696000000004</v>
       </c>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C43" s="2">
         <v>-95820.804999999993</v>
@@ -1783,11 +2420,8 @@
       <c r="D43" s="2">
         <v>-56667.737000000001</v>
       </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
       <c r="H43" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I43" s="2">
         <v>-95844.239000000001</v>
@@ -1795,14 +2429,13 @@
       <c r="J43" s="2">
         <v>-56651.94</v>
       </c>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C44" s="2">
         <v>-95822.732999999993</v>
@@ -1810,11 +2443,8 @@
       <c r="D44" s="2">
         <v>-56667.618000000002</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
       <c r="H44" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I44" s="2">
         <v>-95848.082999999999</v>
@@ -1822,14 +2452,13 @@
       <c r="J44" s="2">
         <v>-56651.553</v>
       </c>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C45" s="2">
         <v>-95821.565000000002</v>
@@ -1837,11 +2466,8 @@
       <c r="D45" s="2">
         <v>-56656.035000000003</v>
       </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
       <c r="H45" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I45" s="2">
         <v>-95845.781000000003</v>
@@ -1849,14 +2475,13 @@
       <c r="J45" s="2">
         <v>-56628.749000000003</v>
       </c>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C46" s="2">
         <v>-95815.365999999995</v>
@@ -1864,11 +2489,8 @@
       <c r="D46" s="2">
         <v>-56650.974999999999</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
       <c r="H46" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I46" s="2">
         <v>-95841.971000000005</v>
@@ -1876,14 +2498,13 @@
       <c r="J46" s="2">
         <v>-56629.133999999998</v>
       </c>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C47" s="2">
         <v>-95799.748999999996</v>
@@ -1891,11 +2512,8 @@
       <c r="D47" s="2">
         <v>-56652.546000000002</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
       <c r="H47" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I47" s="2">
         <v>-95841.41</v>
@@ -1903,14 +2521,13 @@
       <c r="J47" s="2">
         <v>-56623.553</v>
       </c>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C48" s="2">
         <v>-95799.87</v>
@@ -1918,11 +2535,8 @@
       <c r="D48" s="2">
         <v>-56653.387999999999</v>
       </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
       <c r="H48" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I48" s="2">
         <v>-95815.495999999999</v>
@@ -1930,14 +2544,13 @@
       <c r="J48" s="2">
         <v>-56626.186000000002</v>
       </c>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2">
         <v>-95750.01</v>
@@ -1945,11 +2558,8 @@
       <c r="D49" s="2">
         <v>-56658.258000000002</v>
       </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
       <c r="H49" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I49" s="2">
         <v>-95813.020999999993</v>
@@ -1957,14 +2567,13 @@
       <c r="J49" s="2">
         <v>-56628.866000000002</v>
       </c>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C50" s="2">
         <v>-95713.152000000002</v>
@@ -1972,11 +2581,8 @@
       <c r="D50" s="2">
         <v>-56661.540999999997</v>
       </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
       <c r="H50" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="I50" s="2">
         <v>-95801.929000000004</v>
@@ -1984,14 +2590,13 @@
       <c r="J50" s="2">
         <v>-56630.004999999997</v>
       </c>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2">
         <v>-95712.627999999997</v>
@@ -1999,11 +2604,8 @@
       <c r="D51" s="2">
         <v>-56661.341999999997</v>
       </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
       <c r="H51" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I51" s="2">
         <v>-95787.553</v>
@@ -2011,14 +2613,13 @@
       <c r="J51" s="2">
         <v>-56632.286</v>
       </c>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C52" s="2">
         <v>-95665.555999999997</v>
@@ -2026,11 +2627,8 @@
       <c r="D52" s="2">
         <v>-56666.093999999997</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
       <c r="H52" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I52" s="2">
         <v>-95747.823000000004</v>
@@ -2038,14 +2636,13 @@
       <c r="J52" s="2">
         <v>-56636.97</v>
       </c>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C53" s="2">
         <v>-95615.807000000001</v>
@@ -2053,11 +2650,8 @@
       <c r="D53" s="2">
         <v>-56671.114000000001</v>
       </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
       <c r="H53" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I53" s="2">
         <v>-95711.269</v>
@@ -2065,14 +2659,13 @@
       <c r="J53" s="2">
         <v>-56643.205000000002</v>
       </c>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C54" s="2">
         <v>-95566.066999999995</v>
@@ -2080,11 +2673,8 @@
       <c r="D54" s="2">
         <v>-56676.133999999998</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
       <c r="H54" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="I54" s="2">
         <v>-95680.986000000004</v>
@@ -2092,14 +2682,13 @@
       <c r="J54" s="2">
         <v>-56646.254000000001</v>
       </c>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C55" s="2">
         <v>-95516.316999999995</v>
@@ -2107,11 +2696,8 @@
       <c r="D55" s="2">
         <v>-56681.163</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
       <c r="H55" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I55" s="2">
         <v>-95621.286999999997</v>
@@ -2119,14 +2705,13 @@
       <c r="J55" s="2">
         <v>-56652.284</v>
       </c>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="57" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C57" s="2">
         <v>-95466.567999999999</v>
@@ -2134,11 +2719,8 @@
       <c r="D57" s="2">
         <v>-56686.182999999997</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
       <c r="H57" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I57" s="2">
         <v>-95451.157999999996</v>
@@ -2146,14 +2728,13 @@
       <c r="J57" s="2">
         <v>-56669.453000000001</v>
       </c>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C58" s="2">
         <v>-95416.817999999999</v>
@@ -2161,11 +2742,8 @@
       <c r="D58" s="2">
         <v>-56691.203000000001</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
       <c r="H58" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I58" s="2">
         <v>-95264.599000000002</v>
@@ -2173,14 +2751,13 @@
       <c r="J58" s="2">
         <v>-56688.292000000001</v>
       </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C59" s="2">
         <v>-95377.028000000006</v>
@@ -2188,11 +2765,8 @@
       <c r="D59" s="2">
         <v>-56695.222999999998</v>
       </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
       <c r="H59" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I59" s="2">
         <v>-95226.036999999997</v>
@@ -2200,14 +2774,13 @@
       <c r="J59" s="2">
         <v>-56692.184000000001</v>
       </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C60" s="2">
         <v>-95327.278000000006</v>
@@ -2215,11 +2788,8 @@
       <c r="D60" s="2">
         <v>-56700.243000000002</v>
       </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
       <c r="H60" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I60" s="2">
         <v>-95167.29</v>
@@ -2227,14 +2797,13 @@
       <c r="J60" s="2">
         <v>-56697.205000000002</v>
       </c>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C61" s="2">
         <v>-95277.528999999995</v>
@@ -2242,11 +2811,8 @@
       <c r="D61" s="2">
         <v>-56705.262000000002</v>
       </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
       <c r="H61" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2">
         <v>-95126.543000000005</v>
@@ -2254,14 +2820,13 @@
       <c r="J61" s="2">
         <v>-56702.226999999999</v>
       </c>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C62" s="2">
         <v>-95227.862999999998</v>
@@ -2269,11 +2834,8 @@
       <c r="D62" s="2">
         <v>-56710.271999999997</v>
       </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
       <c r="H62" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I62" s="2">
         <v>-95076.796000000002</v>
@@ -2281,14 +2843,13 @@
       <c r="J62" s="2">
         <v>-56707.249000000003</v>
       </c>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C63" s="2">
         <v>-95178.115999999995</v>
@@ -2296,9 +2857,6 @@
       <c r="D63" s="2">
         <v>-56715.294000000002</v>
       </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
       <c r="H63" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,14 +2866,13 @@
       <c r="J63" s="2">
         <v>-56712.271000000001</v>
       </c>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C64" s="2">
         <v>-95128.369000000006</v>
@@ -2323,11 +2880,8 @@
       <c r="D64" s="2">
         <v>-56720.315999999999</v>
       </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
       <c r="H64" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I64" s="2">
         <v>-94977.301999999996</v>
@@ -2335,14 +2889,13 @@
       <c r="J64" s="2">
         <v>-56717.292999999998</v>
       </c>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C65" s="2">
         <v>-95078.622000000003</v>
@@ -2350,11 +2903,8 @@
       <c r="D65" s="2">
         <v>-56725.338000000003</v>
       </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
       <c r="H65" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I65" s="2">
         <v>-94925.565000000002</v>
@@ -2362,14 +2912,13 @@
       <c r="J65" s="2">
         <v>-56722.516000000003</v>
       </c>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C66" s="2">
         <v>-95028.875</v>
@@ -2377,11 +2926,8 @@
       <c r="D66" s="2">
         <v>-56730.36</v>
       </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
       <c r="H66" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I66" s="2">
         <v>-94877.808000000005</v>
@@ -2389,14 +2935,13 @@
       <c r="J66" s="2">
         <v>-56727.336000000003</v>
       </c>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>-94979.127999999997</v>
@@ -2404,11 +2949,8 @@
       <c r="D67" s="2">
         <v>-56735.381999999998</v>
       </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
       <c r="H67" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I67" s="2">
         <v>-94828.061000000002</v>
@@ -2416,14 +2958,13 @@
       <c r="J67" s="2">
         <v>-56732.358</v>
       </c>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C68" s="2">
         <v>-94929.380999999994</v>
@@ -2431,11 +2972,8 @@
       <c r="D68" s="2">
         <v>-56740.404000000002</v>
       </c>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
       <c r="H68" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I68" s="2">
         <v>-94778.313999999998</v>
@@ -2443,14 +2981,13 @@
       <c r="J68" s="2">
         <v>-56737.38</v>
       </c>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C69" s="2">
         <v>-94879.634000000005</v>
@@ -2458,11 +2995,8 @@
       <c r="D69" s="2">
         <v>-56745.425999999999</v>
       </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
       <c r="H69" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I69" s="2">
         <v>-94733.17</v>
@@ -2470,14 +3004,13 @@
       <c r="J69" s="2">
         <v>-56741.936999999998</v>
       </c>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C70" s="2">
         <v>-94829.887000000002</v>
@@ -2485,11 +3018,8 @@
       <c r="D70" s="2">
         <v>-56750.447999999997</v>
       </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
       <c r="H70" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I70" s="2">
         <v>-94713.646999999997</v>
@@ -2497,14 +3027,13 @@
       <c r="J70" s="2">
         <v>-56737.877</v>
       </c>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C71" s="2">
         <v>-94780.14</v>
@@ -2512,11 +3041,8 @@
       <c r="D71" s="2">
         <v>-56755.47</v>
       </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
       <c r="H71" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I71" s="2">
         <v>-94695.301999999996</v>
@@ -2524,14 +3050,13 @@
       <c r="J71" s="2">
         <v>-56737.218999999997</v>
       </c>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C72" s="2">
         <v>-94732.402000000002</v>
@@ -2539,11 +3064,8 @@
       <c r="D72" s="2">
         <v>-56760.288999999997</v>
       </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
       <c r="H72" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="I72" s="2">
         <v>-94655.191999999995</v>
@@ -2551,14 +3073,13 @@
       <c r="J72" s="2">
         <v>-56739.428999999996</v>
       </c>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C73" s="2">
         <v>-94732.521999999997</v>
@@ -2566,11 +3087,8 @@
       <c r="D73" s="2">
         <v>-56761.468999999997</v>
       </c>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
       <c r="H73" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I73" s="2">
         <v>-94656.88</v>
@@ -2578,14 +3096,13 @@
       <c r="J73" s="2">
         <v>-56749.637999999999</v>
       </c>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C74" s="2">
         <v>-94716.312000000005</v>
@@ -2593,11 +3110,8 @@
       <c r="D74" s="2">
         <v>-56763.669000000002</v>
       </c>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
       <c r="H74" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I74" s="2">
         <v>-94650.96</v>
@@ -2605,14 +3119,13 @@
       <c r="J74" s="2">
         <v>-56750.235999999997</v>
       </c>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C75" s="2">
         <v>-94716.13</v>
@@ -2620,11 +3133,8 @@
       <c r="D75" s="2">
         <v>-56761.93</v>
       </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
       <c r="H75" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I75" s="2">
         <v>-94646.274999999994</v>
@@ -2632,14 +3142,13 @@
       <c r="J75" s="2">
         <v>-56756.927000000003</v>
       </c>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C76" s="2">
         <v>-94656.606</v>
@@ -2647,11 +3156,8 @@
       <c r="D76" s="2">
         <v>-56767.938000000002</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
       <c r="H76" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="I76" s="2">
         <v>-94600.922000000006</v>
@@ -2659,14 +3165,13 @@
       <c r="J76" s="2">
         <v>-56761.557999999997</v>
       </c>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C77" s="2">
         <v>-94650.824999999997</v>
@@ -2674,11 +3179,8 @@
       <c r="D77" s="2">
         <v>-56767.548000000003</v>
       </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
       <c r="H77" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I77" s="2">
         <v>-94599.138000000006</v>
@@ -2686,14 +3188,13 @@
       <c r="J77" s="2">
         <v>-56754.457999999999</v>
       </c>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C78" s="2">
         <v>-94647.062999999995</v>
@@ -2701,11 +3202,8 @@
       <c r="D78" s="2">
         <v>-56764.624000000003</v>
       </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
       <c r="H78" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I78" s="2">
         <v>-94586.551000000007</v>
@@ -2713,14 +3211,13 @@
       <c r="J78" s="2">
         <v>-56756.737000000001</v>
       </c>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C79" s="2">
         <v>-94595.603000000003</v>
@@ -2728,11 +3225,8 @@
       <c r="D79" s="2">
         <v>-56769.862000000001</v>
       </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
       <c r="H79" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I79" s="2">
         <v>-94510.99</v>
@@ -2740,14 +3234,13 @@
       <c r="J79" s="2">
         <v>-56764.364000000001</v>
       </c>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C80" s="2">
         <v>-94590.837</v>
@@ -2755,19 +3248,13 @@
       <c r="D80" s="2">
         <v>-56777.631999999998</v>
       </c>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C81" s="2">
         <v>-94551.062999999995</v>
@@ -2775,19 +3262,13 @@
       <c r="D81" s="2">
         <v>-56782.408000000003</v>
       </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C82" s="2">
         <v>-94516.362999999998</v>
@@ -2795,19 +3276,13 @@
       <c r="D82" s="2">
         <v>-56782.097999999998</v>
       </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="84" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C84" s="2">
         <v>-94453.126999999993</v>
@@ -2815,11 +3290,8 @@
       <c r="D84" s="2">
         <v>-56788.476999999999</v>
       </c>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
       <c r="H84" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I84" s="2">
         <v>-94450.796000000002</v>
@@ -2827,14 +3299,13 @@
       <c r="J84" s="2">
         <v>-56770.44</v>
       </c>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C85" s="2">
         <v>-94403.38</v>
@@ -2842,11 +3313,8 @@
       <c r="D85" s="2">
         <v>-56793.498</v>
       </c>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
       <c r="H85" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I85" s="2">
         <v>-94401.546000000002</v>
@@ -2854,14 +3322,13 @@
       <c r="J85" s="2">
         <v>-56775.411</v>
       </c>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C86" s="2">
         <v>-94353.633000000002</v>
@@ -2869,11 +3336,8 @@
       <c r="D86" s="2">
         <v>-56798.52</v>
       </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
       <c r="H86" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I86" s="2">
         <v>-94351.798999999999</v>
@@ -2881,14 +3345,13 @@
       <c r="J86" s="2">
         <v>-56780.432999999997</v>
       </c>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C87" s="2">
         <v>-94303.885999999999</v>
@@ -2896,11 +3359,8 @@
       <c r="D87" s="2">
         <v>-56803.540999999997</v>
       </c>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
       <c r="H87" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I87" s="2">
         <v>-94302.051999999996</v>
@@ -2908,14 +3368,13 @@
       <c r="J87" s="2">
         <v>-56785.453999999998</v>
       </c>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C88" s="2">
         <v>-94254.138000000006</v>
@@ -2923,11 +3382,8 @@
       <c r="D88" s="2">
         <v>-56808.563000000002</v>
       </c>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
       <c r="H88" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I88" s="2">
         <v>-94252.304000000004</v>
@@ -2935,14 +3391,13 @@
       <c r="J88" s="2">
         <v>-56790.476000000002</v>
       </c>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C89" s="2">
         <v>-94204.391000000003</v>
@@ -2950,11 +3405,8 @@
       <c r="D89" s="2">
         <v>-56813.584000000003</v>
       </c>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
       <c r="H89" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I89" s="2">
         <v>-94202.557000000001</v>
@@ -2962,14 +3414,13 @@
       <c r="J89" s="2">
         <v>-56795.497000000003</v>
       </c>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C90" s="2">
         <v>-94154.644</v>
@@ -2977,9 +3428,6 @@
       <c r="D90" s="2">
         <v>-56818.606</v>
       </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
       <c r="H90" s="1" t="s">
         <v>29</v>
       </c>
@@ -2989,14 +3437,13 @@
       <c r="J90" s="2">
         <v>-56800.519</v>
       </c>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C91" s="2">
         <v>-94136.555999999997</v>
@@ -3004,11 +3451,8 @@
       <c r="D91" s="2">
         <v>-56820.432000000001</v>
       </c>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
       <c r="H91" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I91" s="2">
         <v>-94134.721999999994</v>
@@ -3016,14 +3460,13 @@
       <c r="J91" s="2">
         <v>-56802.343999999997</v>
       </c>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C92" s="2">
         <v>-94086.808999999994</v>
@@ -3031,11 +3474,8 @@
       <c r="D92" s="2">
         <v>-56825.453000000001</v>
       </c>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
       <c r="H92" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I92" s="2">
         <v>-94084.975000000006</v>
@@ -3043,14 +3483,13 @@
       <c r="J92" s="2">
         <v>-56807.364999999998</v>
       </c>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C93" s="2">
         <v>-94037.062000000005</v>
@@ -3058,11 +3497,8 @@
       <c r="D93" s="2">
         <v>-56830.474999999999</v>
       </c>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
       <c r="H93" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I93" s="2">
         <v>-94035.228000000003</v>
@@ -3070,14 +3506,13 @@
       <c r="J93" s="2">
         <v>-56812.387000000002</v>
       </c>
-      <c r="K93" s="2"/>
-    </row>
-    <row r="94" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C94" s="2">
         <v>-93987.313999999998</v>
@@ -3085,11 +3520,8 @@
       <c r="D94" s="2">
         <v>-56835.495999999999</v>
       </c>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
       <c r="H94" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I94" s="2">
         <v>-93985.48</v>
@@ -3097,14 +3529,13 @@
       <c r="J94" s="2">
         <v>-56817.408000000003</v>
       </c>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C95" s="2">
         <v>-93949.804999999993</v>
@@ -3112,11 +3543,8 @@
       <c r="D95" s="2">
         <v>-56839.283000000003</v>
       </c>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
       <c r="H95" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I95" s="2">
         <v>-93935.732999999993</v>
@@ -3124,14 +3552,13 @@
       <c r="J95" s="2">
         <v>-56822.43</v>
       </c>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C96" s="2">
         <v>-93887.82</v>
@@ -3139,11 +3566,8 @@
       <c r="D96" s="2">
         <v>-56845.538999999997</v>
       </c>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
       <c r="H96" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I96" s="2">
         <v>-93885.986000000004</v>
@@ -3151,14 +3575,13 @@
       <c r="J96" s="2">
         <v>-56827.451000000001</v>
       </c>
-      <c r="K96" s="2"/>
-    </row>
-    <row r="97" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C97" s="2">
         <v>-93838.073000000004</v>
@@ -3166,11 +3589,8 @@
       <c r="D97" s="2">
         <v>-56850.559999999998</v>
       </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
       <c r="H97" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I97" s="2">
         <v>-93836.239000000001</v>
@@ -3178,14 +3598,13 @@
       <c r="J97" s="2">
         <v>-56832.472999999998</v>
       </c>
-      <c r="K97" s="2"/>
-    </row>
-    <row r="98" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C98" s="2">
         <v>-93803.648000000001</v>
@@ -3193,11 +3612,8 @@
       <c r="D98" s="2">
         <v>-56854.035000000003</v>
       </c>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
       <c r="H98" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I98" s="2">
         <v>-93786.491999999998</v>
@@ -3205,14 +3621,13 @@
       <c r="J98" s="2">
         <v>-56837.493999999999</v>
       </c>
-      <c r="K98" s="2"/>
-    </row>
-    <row r="99" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C99" s="2">
         <v>-93744.846999999994</v>
@@ -3220,11 +3635,8 @@
       <c r="D99" s="2">
         <v>-56859.970999999998</v>
       </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
       <c r="H99" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="I99" s="2">
         <v>-93736.744000000006</v>
@@ -3232,14 +3644,13 @@
       <c r="J99" s="2">
         <v>-56842.516000000003</v>
       </c>
-      <c r="K99" s="2"/>
-    </row>
-    <row r="100" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C100" s="2">
         <v>-93689.726999999999</v>
@@ -3247,11 +3658,8 @@
       <c r="D100" s="2">
         <v>-56865.534</v>
       </c>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
       <c r="H100" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I100" s="2">
         <v>-93688.986999999994</v>
@@ -3259,14 +3667,13 @@
       <c r="J100" s="2">
         <v>-56847.336000000003</v>
       </c>
-      <c r="K100" s="2"/>
-    </row>
-    <row r="101" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C101" s="2">
         <v>-93643.063999999998</v>
@@ -3274,11 +3681,8 @@
       <c r="D101" s="2">
         <v>-56870.243999999999</v>
       </c>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
       <c r="H101" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I101" s="2">
         <v>-93641.23</v>
@@ -3286,14 +3690,13 @@
       <c r="J101" s="2">
         <v>-56852.156999999999</v>
       </c>
-      <c r="K101" s="2"/>
-    </row>
-    <row r="102" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C102" s="2">
         <v>-93593.154999999999</v>
@@ -3301,11 +3704,8 @@
       <c r="D102" s="2">
         <v>-56875.281999999999</v>
       </c>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
       <c r="H102" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="I102" s="2">
         <v>-93591.316000000006</v>
@@ -3313,14 +3713,13 @@
       <c r="J102" s="2">
         <v>-56857.195</v>
       </c>
-      <c r="K102" s="2"/>
-    </row>
-    <row r="103" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C103" s="2">
         <v>-93575.066999999995</v>
@@ -3328,11 +3727,8 @@
       <c r="D103" s="2">
         <v>-56877.107000000004</v>
       </c>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
       <c r="H103" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="I103" s="2">
         <v>-93586.289000000004</v>
@@ -3340,14 +3736,13 @@
       <c r="J103" s="2">
         <v>-56807.447999999997</v>
       </c>
-      <c r="K103" s="2"/>
-    </row>
-    <row r="104" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C104" s="2">
         <v>-93573.228000000003</v>
@@ -3355,19 +3750,13 @@
       <c r="D104" s="2">
         <v>-56859.021000000001</v>
       </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-    </row>
-    <row r="105" spans="1:11" s="1" customFormat="1">
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" s="3" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C105" s="2">
         <v>-93568.201000000001</v>
@@ -3375,16 +3764,5185 @@
       <c r="D105" s="2">
         <v>-56809.273999999998</v>
       </c>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" s="2">
+        <v>-93563.172999999995</v>
+      </c>
+      <c r="D107" s="2">
+        <v>-56759.527999999998</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="2">
+        <v>-93581.260999999999</v>
+      </c>
+      <c r="J107" s="2">
+        <v>-56757.701999999997</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" s="2">
+        <v>-93558.145999999993</v>
+      </c>
+      <c r="D108" s="2">
+        <v>-56709.781000000003</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="2">
+        <v>-93576.233999999997</v>
+      </c>
+      <c r="J108" s="2">
+        <v>-56707.955000000002</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="2">
+        <v>-93553.119000000006</v>
+      </c>
+      <c r="D109" s="2">
+        <v>-56660.035000000003</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I109" s="2">
+        <v>-93571.206999999995</v>
+      </c>
+      <c r="J109" s="2">
+        <v>-56658.209000000003</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" s="2">
+        <v>-93548.091</v>
+      </c>
+      <c r="D110" s="2">
+        <v>-56610.288</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I110" s="2">
+        <v>-93566.18</v>
+      </c>
+      <c r="J110" s="2">
+        <v>-56608.462</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="2">
+        <v>-93543.063999999998</v>
+      </c>
+      <c r="D111" s="2">
+        <v>-56560.540999999997</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I111" s="2">
+        <v>-93561.152000000002</v>
+      </c>
+      <c r="J111" s="2">
+        <v>-56558.714999999997</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" s="2">
+        <v>-93538.036999999997</v>
+      </c>
+      <c r="D112" s="2">
+        <v>-56510.794999999998</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" s="2">
+        <v>-93556.125</v>
+      </c>
+      <c r="J112" s="2">
+        <v>-56508.968999999997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="2">
+        <v>-93532.959000000003</v>
+      </c>
+      <c r="D113" s="2">
+        <v>-56460.550999999999</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I113" s="2">
+        <v>-93551.097999999998</v>
+      </c>
+      <c r="J113" s="2">
+        <v>-56459.222000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114" s="2">
+        <v>-93527.982000000004</v>
+      </c>
+      <c r="D114" s="2">
+        <v>-56411.300999999999</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I114" s="2">
+        <v>-93546.07</v>
+      </c>
+      <c r="J114" s="2">
+        <v>-56409.474999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" s="2">
+        <v>-93522.955000000002</v>
+      </c>
+      <c r="D115" s="2">
+        <v>-56361.555</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I115" s="2">
+        <v>-93541.043000000005</v>
+      </c>
+      <c r="J115" s="2">
+        <v>-56359.728999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116" s="2">
+        <v>-93518.337</v>
+      </c>
+      <c r="D116" s="2">
+        <v>-56315.86</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116" s="2">
+        <v>-93536.425000000003</v>
+      </c>
+      <c r="J116" s="2">
+        <v>-56314.031000000003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C117" s="2">
+        <v>-93516.479999999996</v>
+      </c>
+      <c r="D117" s="2">
+        <v>-56297.756000000001</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I117" s="2">
+        <v>-93534.578999999998</v>
+      </c>
+      <c r="J117" s="2">
+        <v>-56295.934000000001</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C118" s="2">
+        <v>-93513.006999999998</v>
+      </c>
+      <c r="D118" s="2">
+        <v>-56263.635999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" s="2">
+        <v>-93510.297000000006</v>
+      </c>
+      <c r="D119" s="2">
+        <v>-56263.705999999998</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I119" s="2">
+        <v>-93527.476999999999</v>
+      </c>
+      <c r="J119" s="2">
+        <v>-56225.896999999997</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C120" s="2">
+        <v>-93509.337</v>
+      </c>
+      <c r="D120" s="2">
+        <v>-56255.275999999998</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I120" s="2">
+        <v>-93523.937999999995</v>
+      </c>
+      <c r="J120" s="2">
+        <v>-56191.476999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C121" s="2">
+        <v>-93507.167000000001</v>
+      </c>
+      <c r="D121" s="2">
+        <v>-56236.375999999997</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I121" s="2">
+        <v>-93520.388000000006</v>
+      </c>
+      <c r="J121" s="2">
+        <v>-56156.656999999999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C122" s="2">
+        <v>-93503.097999999998</v>
+      </c>
+      <c r="D122" s="2">
+        <v>-56193.377</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I122" s="2">
+        <v>-93516.838000000003</v>
+      </c>
+      <c r="J122" s="2">
+        <v>-56121.838000000003</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C123" s="2">
+        <v>-93499.937999999995</v>
+      </c>
+      <c r="D123" s="2">
+        <v>-56158.737000000001</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I123" s="2">
+        <v>-93513.288</v>
+      </c>
+      <c r="J123" s="2">
+        <v>-56087.017999999996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C124" s="2">
+        <v>-93496.448000000004</v>
+      </c>
+      <c r="D124" s="2">
+        <v>-56122.908000000003</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I124" s="2">
+        <v>-93509.748000000007</v>
+      </c>
+      <c r="J124" s="2">
+        <v>-56052.197999999997</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C125" s="2">
+        <v>-93494.678</v>
+      </c>
+      <c r="D125" s="2">
+        <v>-56103.398000000001</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I125" s="2">
+        <v>-93507.718999999997</v>
+      </c>
+      <c r="J125" s="2">
+        <v>-56032.298999999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C126" s="2">
+        <v>-93493.918000000005</v>
+      </c>
+      <c r="D126" s="2">
+        <v>-56094.998</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I126" s="2">
+        <v>-93498.479000000007</v>
+      </c>
+      <c r="J126" s="2">
+        <v>-55941.54</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C127" s="2">
+        <v>-93492.207999999999</v>
+      </c>
+      <c r="D127" s="2">
+        <v>-56076.078000000001</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I127" s="2">
+        <v>-93495.438999999998</v>
+      </c>
+      <c r="J127" s="2">
+        <v>-55911.7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C128" s="2">
+        <v>-93489.498999999996</v>
+      </c>
+      <c r="D128" s="2">
+        <v>-56046.197999999997</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I128" s="2">
+        <v>-93492.4</v>
+      </c>
+      <c r="J128" s="2">
+        <v>-55881.85</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C129" s="2">
+        <v>-93487.698999999993</v>
+      </c>
+      <c r="D129" s="2">
+        <v>-56026.279000000002</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I129" s="2">
+        <v>-93488.34</v>
+      </c>
+      <c r="J129" s="2">
+        <v>-55842.061000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C130" s="2">
+        <v>-93488.819000000003</v>
+      </c>
+      <c r="D130" s="2">
+        <v>-56026.169000000002</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I130" s="2">
+        <v>-93486.264999999999</v>
+      </c>
+      <c r="J130" s="2">
+        <v>-55821.692999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C131" s="2">
+        <v>-93487.899000000005</v>
+      </c>
+      <c r="D131" s="2">
+        <v>-56017.129000000001</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I131" s="2">
+        <v>-93484.79</v>
+      </c>
+      <c r="J131" s="2">
+        <v>-55807.241000000002</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C132" s="2">
+        <v>-93486.888999999996</v>
+      </c>
+      <c r="D132" s="2">
+        <v>-56017.228999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C133" s="2">
+        <v>-93483.739000000001</v>
+      </c>
+      <c r="D133" s="2">
+        <v>-55982.478999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C134" s="2">
+        <v>-93479.489000000001</v>
+      </c>
+      <c r="D134" s="2">
+        <v>-55943.47</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C135" s="2">
+        <v>-93476.239000000001</v>
+      </c>
+      <c r="D135" s="2">
+        <v>-55913.66</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C136" s="2">
+        <v>-93475.213000000003</v>
+      </c>
+      <c r="D136" s="2">
+        <v>-55904.196000000004</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C137" s="2">
+        <v>-93468.826000000001</v>
+      </c>
+      <c r="D137" s="2">
+        <v>-55879.207000000002</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C138" s="2">
+        <v>-93467.337</v>
+      </c>
+      <c r="D138" s="2">
+        <v>-55864.281000000003</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C139" s="2">
+        <v>-93465.75</v>
+      </c>
+      <c r="D139" s="2">
+        <v>-55837.550999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C140" s="2">
+        <v>-93464.668999999994</v>
+      </c>
+      <c r="D140" s="2">
+        <v>-55825.972000000002</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C141" s="2">
+        <v>-93462.664000000004</v>
+      </c>
+      <c r="D141" s="2">
+        <v>-55804.504000000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" s="2">
+        <v>-93462.03</v>
+      </c>
+      <c r="D143" s="2">
+        <v>-55797.720999999998</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143" s="2">
+        <v>-93484.062999999995</v>
+      </c>
+      <c r="J143" s="2">
+        <v>-55800.055999999997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144" s="2">
+        <v>-93463.51</v>
+      </c>
+      <c r="D144" s="2">
+        <v>-55792.550999999999</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" s="2">
+        <v>-93481.75</v>
+      </c>
+      <c r="J144" s="2">
+        <v>-55777.392</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C145" s="2">
+        <v>-93459.66</v>
+      </c>
+      <c r="D145" s="2">
+        <v>-55754.482000000004</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I145" s="2">
+        <v>-93479.22</v>
+      </c>
+      <c r="J145" s="2">
+        <v>-55752.521999999997</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C146" s="2">
+        <v>-93456.781000000003</v>
+      </c>
+      <c r="D146" s="2">
+        <v>-55736.491999999998</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I146" s="2">
+        <v>-93477.39</v>
+      </c>
+      <c r="J146" s="2">
+        <v>-55734.421999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="2">
+        <v>-93454.251000000004</v>
+      </c>
+      <c r="D147" s="2">
+        <v>-55704.942000000003</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I147" s="2">
+        <v>-93471.313999999998</v>
+      </c>
+      <c r="J147" s="2">
+        <v>-55673.792999999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" s="2">
+        <v>-93451.448999999993</v>
+      </c>
+      <c r="D148" s="2">
+        <v>-55674.531000000003</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I148" s="2">
+        <v>-93469.434999999998</v>
+      </c>
+      <c r="J148" s="2">
+        <v>-55655.044000000002</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C149" s="2">
+        <v>-93450.591</v>
+      </c>
+      <c r="D149" s="2">
+        <v>-55665.222999999998</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" s="2">
+        <v>-93468.57</v>
+      </c>
+      <c r="J149" s="2">
+        <v>-55646.411999999997</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" s="2">
+        <v>-93449.917000000001</v>
+      </c>
+      <c r="D150" s="2">
+        <v>-55656.741999999998</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I150" s="2">
+        <v>-93466.770999999993</v>
+      </c>
+      <c r="J150" s="2">
+        <v>-55628.442999999999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C151" s="2">
+        <v>-93449.115999999995</v>
+      </c>
+      <c r="D151" s="2">
+        <v>-55646.661999999997</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I151" s="2">
+        <v>-93455.801999999996</v>
+      </c>
+      <c r="J151" s="2">
+        <v>-55508.995000000003</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152" s="2">
+        <v>-93447.111000000004</v>
+      </c>
+      <c r="D152" s="2">
+        <v>-55621.442999999999</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I152" s="2">
+        <v>-93444.832999999999</v>
+      </c>
+      <c r="J152" s="2">
+        <v>-55409.546000000002</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C153" s="2">
+        <v>-93442.771999999997</v>
+      </c>
+      <c r="D153" s="2">
+        <v>-55575.764000000003</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I153" s="2">
+        <v>-93433.862999999998</v>
+      </c>
+      <c r="J153" s="2">
+        <v>-55300.097000000002</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C154" s="2">
+        <v>-93438.782000000007</v>
+      </c>
+      <c r="D154" s="2">
+        <v>-55533.444000000003</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I154" s="2">
+        <v>-93422.894</v>
+      </c>
+      <c r="J154" s="2">
+        <v>-55190.648999999998</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C155" s="2">
+        <v>-93433.712</v>
+      </c>
+      <c r="D155" s="2">
+        <v>-55483.754999999997</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I155" s="2">
+        <v>-93421.084000000003</v>
+      </c>
+      <c r="J155" s="2">
+        <v>-55172.559000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C156" s="2">
+        <v>-93428.482999999993</v>
+      </c>
+      <c r="D156" s="2">
+        <v>-55435.065999999999</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I156" s="2">
+        <v>-93414.884999999995</v>
+      </c>
+      <c r="J156" s="2">
+        <v>-55110.508999999998</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C157" s="2">
+        <v>-93423.553</v>
+      </c>
+      <c r="D157" s="2">
+        <v>-55387.305999999997</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I157" s="2">
+        <v>-93402.835000000006</v>
+      </c>
+      <c r="J157" s="2">
+        <v>-54990.110999999997</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C158" s="2">
+        <v>-93418.312999999995</v>
+      </c>
+      <c r="D158" s="2">
+        <v>-55337.607000000004</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I158" s="2">
+        <v>-93393.885999999999</v>
+      </c>
+      <c r="J158" s="2">
+        <v>-54900.561999999998</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C159" s="2">
+        <v>-93418.312999999995</v>
+      </c>
+      <c r="D159" s="2">
+        <v>-55337.607000000004</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C160" s="2">
+        <v>-93416.263000000006</v>
+      </c>
+      <c r="D160" s="2">
+        <v>-55318.786999999997</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C161" s="2">
+        <v>-93410.793999999994</v>
+      </c>
+      <c r="D161" s="2">
+        <v>-55269.148000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C162" s="2">
+        <v>-93406.123999999996</v>
+      </c>
+      <c r="D162" s="2">
+        <v>-55223.438000000002</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C163" s="2">
+        <v>-93401.534</v>
+      </c>
+      <c r="D163" s="2">
+        <v>-55174.519</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C164" s="2">
+        <v>-93399.573999999993</v>
+      </c>
+      <c r="D164" s="2">
+        <v>-55157.688999999998</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C165" s="2">
+        <v>-93395.843999999997</v>
+      </c>
+      <c r="D165" s="2">
+        <v>-55140.349000000002</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C166" s="2">
+        <v>-93394.625</v>
+      </c>
+      <c r="D166" s="2">
+        <v>-55126.919000000002</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C167" s="2">
+        <v>-93394.755000000005</v>
+      </c>
+      <c r="D167" s="2">
+        <v>-55102.419000000002</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C168" s="2">
+        <v>-93390.494999999995</v>
+      </c>
+      <c r="D168" s="2">
+        <v>-55061.15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C169" s="2">
+        <v>-93385.285000000003</v>
+      </c>
+      <c r="D169" s="2">
+        <v>-55011.55</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C170" s="2">
+        <v>-93380.145000000004</v>
+      </c>
+      <c r="D170" s="2">
+        <v>-54961.970999999998</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C171" s="2">
+        <v>-93374.966</v>
+      </c>
+      <c r="D171" s="2">
+        <v>-54913.182000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C172" s="2">
+        <v>-93376.856</v>
+      </c>
+      <c r="D172" s="2">
+        <v>-54912.991999999998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C173" s="2">
+        <v>-93375.956000000006</v>
+      </c>
+      <c r="D173" s="2">
+        <v>-54903.942000000003</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C174" s="2">
+        <v>-93374.115999999995</v>
+      </c>
+      <c r="D174" s="2">
+        <v>-54885.572</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C175" s="2">
+        <v>-93371.665999999997</v>
+      </c>
+      <c r="D175" s="2">
+        <v>-54885.682000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C177" s="2">
+        <v>-93362.525999999998</v>
+      </c>
+      <c r="D177" s="2">
+        <v>-54795.002999999997</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I177" s="2">
+        <v>-93380.455000000002</v>
+      </c>
+      <c r="J177" s="2">
+        <v>-54766.232000000004</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" s="2">
+        <v>-93354.896999999997</v>
+      </c>
+      <c r="D178" s="2">
+        <v>-54716.184000000001</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I178" s="2">
+        <v>-93372.993000000002</v>
+      </c>
+      <c r="J178" s="2">
+        <v>-54691.603999999999</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179" s="2">
+        <v>-93350.297000000006</v>
+      </c>
+      <c r="D179" s="2">
+        <v>-54694.444000000003</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I179" s="2">
+        <v>-93365.076000000001</v>
+      </c>
+      <c r="J179" s="2">
+        <v>-54612.425000000003</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180" s="2">
+        <v>-93348.676999999996</v>
+      </c>
+      <c r="D180" s="2">
+        <v>-54675.614000000001</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I180" s="2">
+        <v>-93265.570999999996</v>
+      </c>
+      <c r="J180" s="2">
+        <v>-54622.360999999997</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C181" s="2">
+        <v>-93348.726999999999</v>
+      </c>
+      <c r="D181" s="2">
+        <v>-54655.093999999997</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I181" s="2">
+        <v>-93159.1</v>
+      </c>
+      <c r="J181" s="2">
+        <v>-54632.991000000002</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C182" s="2">
+        <v>-93348.092000000004</v>
+      </c>
+      <c r="D182" s="2">
+        <v>-54648.894</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I182" s="2">
+        <v>-93089.135999999999</v>
+      </c>
+      <c r="J182" s="2">
+        <v>-54639.976999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" s="2">
+        <v>-93350.428</v>
+      </c>
+      <c r="D183" s="2">
+        <v>-54648.665000000001</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I183" s="2">
+        <v>-93020.040999999997</v>
+      </c>
+      <c r="J183" s="2">
+        <v>-54646.877</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C184" s="2">
+        <v>-93348.793999999994</v>
+      </c>
+      <c r="D184" s="2">
+        <v>-54632.322</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I184" s="2">
+        <v>-92957.566999999995</v>
+      </c>
+      <c r="J184" s="2">
+        <v>-54653.114000000001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C185" s="2">
+        <v>-93337.837</v>
+      </c>
+      <c r="D185" s="2">
+        <v>-54633.415999999997</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I185" s="2">
+        <v>-92881.717000000004</v>
+      </c>
+      <c r="J185" s="2">
+        <v>-54660.688000000002</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="A186" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C186" s="2">
+        <v>-93181.528000000006</v>
+      </c>
+      <c r="D186" s="2">
+        <v>-54649.023000000001</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I186" s="2">
+        <v>-92807.841</v>
+      </c>
+      <c r="J186" s="2">
+        <v>-54668.065000000002</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="A187" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C187" s="2">
+        <v>-93101.445999999996</v>
+      </c>
+      <c r="D187" s="2">
+        <v>-54657.02</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I187" s="2">
+        <v>-92801.653000000006</v>
+      </c>
+      <c r="J187" s="2">
+        <v>-54662.993999999999</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="A188" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C188" s="2">
+        <v>-93021.846999999994</v>
+      </c>
+      <c r="D188" s="2">
+        <v>-54664.966999999997</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C189" s="2">
+        <v>-92954.226999999999</v>
+      </c>
+      <c r="D189" s="2">
+        <v>-54671.718999999997</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12">
+      <c r="A190" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C190" s="2">
+        <v>-92849.817999999999</v>
+      </c>
+      <c r="D190" s="2">
+        <v>-54682.144</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C191" s="2">
+        <v>-92806.513000000006</v>
+      </c>
+      <c r="D191" s="2">
+        <v>-54686.468000000001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C192" s="2">
+        <v>-92788.422999999995</v>
+      </c>
+      <c r="D192" s="2">
+        <v>-54688.275000000001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C193" s="2">
+        <v>-92786.641000000003</v>
+      </c>
+      <c r="D193" s="2">
+        <v>-54670.180999999997</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C195" s="2">
+        <v>-92756.523000000001</v>
+      </c>
+      <c r="D195" s="2">
+        <v>-54390.3</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I195" s="2">
+        <v>-92774.612999999998</v>
+      </c>
+      <c r="J195" s="2">
+        <v>-54388.49</v>
+      </c>
+      <c r="L195" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C196" s="2">
+        <v>-92750.153999999995</v>
+      </c>
+      <c r="D196" s="2">
+        <v>-54325.610999999997</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I196" s="2">
+        <v>-92770.843999999997</v>
+      </c>
+      <c r="J196" s="2">
+        <v>-54350.17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" s="2">
+        <v>-92745.255000000005</v>
+      </c>
+      <c r="D197" s="2">
+        <v>-54275.851999999999</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I197" s="2">
+        <v>-92766.873999999996</v>
+      </c>
+      <c r="J197" s="2">
+        <v>-54309.870999999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C198" s="2">
+        <v>-92740.054999999993</v>
+      </c>
+      <c r="D198" s="2">
+        <v>-54223.103000000003</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" s="2">
+        <v>-92762.414999999994</v>
+      </c>
+      <c r="J198" s="2">
+        <v>-54264.591999999997</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C199" s="2">
+        <v>-92735.106</v>
+      </c>
+      <c r="D199" s="2">
+        <v>-54172.853999999999</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I199" s="2">
+        <v>-92757.815000000002</v>
+      </c>
+      <c r="J199" s="2">
+        <v>-54217.913</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C200" s="2">
+        <v>-92730.554999999993</v>
+      </c>
+      <c r="D200" s="2">
+        <v>-54126.612999999998</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I200" s="2">
+        <v>-92751.625</v>
+      </c>
+      <c r="J200" s="2">
+        <v>-54155.123</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C201" s="2">
+        <v>-92680.796000000002</v>
+      </c>
+      <c r="D201" s="2">
+        <v>-54131.574000000001</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I201" s="2">
+        <v>-92746.854999999996</v>
+      </c>
+      <c r="J201" s="2">
+        <v>-54106.703000000001</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12">
+      <c r="A202" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C202" s="2">
+        <v>-92631.046000000002</v>
+      </c>
+      <c r="D202" s="2">
+        <v>-54136.544000000002</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I202" s="2">
+        <v>-92697.104999999996</v>
+      </c>
+      <c r="J202" s="2">
+        <v>-54111.673000000003</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12">
+      <c r="A203" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C203" s="2">
+        <v>-92581.297000000006</v>
+      </c>
+      <c r="D203" s="2">
+        <v>-54141.504000000001</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I203" s="2">
+        <v>-92652.826000000001</v>
+      </c>
+      <c r="J203" s="2">
+        <v>-54116.093999999997</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12">
+      <c r="A204" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C204" s="2">
+        <v>-92548.157000000007</v>
+      </c>
+      <c r="D204" s="2">
+        <v>-54144.815000000002</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I204" s="2">
+        <v>-92602.576000000001</v>
+      </c>
+      <c r="J204" s="2">
+        <v>-54121.103999999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12">
+      <c r="A205" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C205" s="2">
+        <v>-92501.687999999995</v>
+      </c>
+      <c r="D205" s="2">
+        <v>-54149.455000000002</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I205" s="2">
+        <v>-92558.297000000006</v>
+      </c>
+      <c r="J205" s="2">
+        <v>-54125.523999999998</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12">
+      <c r="A206" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C206" s="2">
+        <v>-92458.607999999993</v>
+      </c>
+      <c r="D206" s="2">
+        <v>-54153.754999999997</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I206" s="2">
+        <v>-92506.357000000004</v>
+      </c>
+      <c r="J206" s="2">
+        <v>-54130.714999999997</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
+      <c r="A207" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C207" s="2">
+        <v>-92412.138999999996</v>
+      </c>
+      <c r="D207" s="2">
+        <v>-54158.396000000001</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I207" s="2">
+        <v>-92458.297999999995</v>
+      </c>
+      <c r="J207" s="2">
+        <v>-54135.504999999997</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12">
+      <c r="A208" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C208" s="2">
+        <v>-92370.349000000002</v>
+      </c>
+      <c r="D208" s="2">
+        <v>-54162.565999999999</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I208" s="2">
+        <v>-92408.548999999999</v>
+      </c>
+      <c r="J208" s="2">
+        <v>-54140.476000000002</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C209" s="2">
+        <v>-92325.57</v>
+      </c>
+      <c r="D209" s="2">
+        <v>-54167.036999999997</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I209" s="2">
+        <v>-92361.778999999995</v>
+      </c>
+      <c r="J209" s="2">
+        <v>-54145.146000000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C210" s="2">
+        <v>-92273.83</v>
+      </c>
+      <c r="D210" s="2">
+        <v>-54172.197</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I210" s="2">
+        <v>-92312.02</v>
+      </c>
+      <c r="J210" s="2">
+        <v>-54150.107000000004</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C211" s="2">
+        <v>-92224.070999999996</v>
+      </c>
+      <c r="D211" s="2">
+        <v>-54177.167000000001</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I211" s="2">
+        <v>-92275.7</v>
+      </c>
+      <c r="J211" s="2">
+        <v>-54153.737000000001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C212" s="2">
+        <v>-92186.191000000006</v>
+      </c>
+      <c r="D212" s="2">
+        <v>-54180.947999999997</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I212" s="2">
+        <v>-92226.451000000001</v>
+      </c>
+      <c r="J212" s="2">
+        <v>-54158.646999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C213" s="2">
+        <v>-92164.660999999993</v>
+      </c>
+      <c r="D213" s="2">
+        <v>-54183.078000000001</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I213" s="2">
+        <v>-92183.460999999996</v>
+      </c>
+      <c r="J213" s="2">
+        <v>-54162.947999999997</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C214" s="2">
+        <v>-92162.691999999995</v>
+      </c>
+      <c r="D214" s="2">
+        <v>-54163.027999999998</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I214" s="2">
+        <v>-92176.3</v>
+      </c>
+      <c r="J214" s="2">
+        <v>-54089.427000000003</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C215" s="2">
+        <v>-92157.15</v>
+      </c>
+      <c r="D215" s="2">
+        <v>-54106.747000000003</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C216" s="2">
+        <v>-92151.599000000002</v>
+      </c>
+      <c r="D216" s="2">
+        <v>-54050.466</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C217" s="2">
+        <v>-92151.858999999997</v>
+      </c>
+      <c r="D217" s="2">
+        <v>-54048.966</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C219" s="2">
+        <v>-92146.788</v>
+      </c>
+      <c r="D219" s="2">
+        <v>-53996.226000000002</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I219" s="2">
+        <v>-92169.998999999996</v>
+      </c>
+      <c r="J219" s="2">
+        <v>-54024.735999999997</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C220" s="2">
+        <v>-92141.717000000004</v>
+      </c>
+      <c r="D220" s="2">
+        <v>-53943.495000000003</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I220" s="2">
+        <v>-92166.127999999997</v>
+      </c>
+      <c r="J220" s="2">
+        <v>-53984.845000000001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C221" s="2">
+        <v>-92136.656000000003</v>
+      </c>
+      <c r="D221" s="2">
+        <v>-53890.754000000001</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I221" s="2">
+        <v>-92161.087</v>
+      </c>
+      <c r="J221" s="2">
+        <v>-53933.105000000003</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C222" s="2">
+        <v>-92131.585000000006</v>
+      </c>
+      <c r="D222" s="2">
+        <v>-53838.023000000001</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I222" s="2">
+        <v>-92155.766000000003</v>
+      </c>
+      <c r="J222" s="2">
+        <v>-53878.423999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C223" s="2">
+        <v>-92126.513999999996</v>
+      </c>
+      <c r="D223" s="2">
+        <v>-53785.283000000003</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I223" s="2">
+        <v>-92153.675000000003</v>
+      </c>
+      <c r="J223" s="2">
+        <v>-53856.993000000002</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C224" s="2">
+        <v>-92128.414000000004</v>
+      </c>
+      <c r="D224" s="2">
+        <v>-53785.101999999999</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I224" s="2">
+        <v>-92148.834000000003</v>
+      </c>
+      <c r="J224" s="2">
+        <v>-53807.222999999998</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C225" s="2">
+        <v>-92119.282000000007</v>
+      </c>
+      <c r="D225" s="2">
+        <v>-53725.962</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I225" s="2">
+        <v>-92146.504000000001</v>
+      </c>
+      <c r="J225" s="2">
+        <v>-53783.302000000003</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C226" s="2">
+        <v>-92117.262000000002</v>
+      </c>
+      <c r="D226" s="2">
+        <v>-53718.271999999997</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I226" s="2">
+        <v>-92143.993000000002</v>
+      </c>
+      <c r="J226" s="2">
+        <v>-53757.451999999997</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="A227" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C227" s="2">
+        <v>-92111.691000000006</v>
+      </c>
+      <c r="D227" s="2">
+        <v>-53668.580999999998</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I227" s="2">
+        <v>-92139.152000000002</v>
+      </c>
+      <c r="J227" s="2">
+        <v>-53707.680999999997</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C228" s="2">
+        <v>-92106.37</v>
+      </c>
+      <c r="D228" s="2">
+        <v>-53621.11</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I228" s="2">
+        <v>-92131.199999999997</v>
+      </c>
+      <c r="J228" s="2">
+        <v>-53618.68</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C229" s="2">
+        <v>-92104.17</v>
+      </c>
+      <c r="D229" s="2">
+        <v>-53603.08</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I229" s="2">
+        <v>-92142.43</v>
+      </c>
+      <c r="J229" s="2">
+        <v>-53617.56</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C230" s="2">
+        <v>-92099.849000000002</v>
+      </c>
+      <c r="D230" s="2">
+        <v>-53567.078999999998</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I230" s="2">
+        <v>-92139.83</v>
+      </c>
+      <c r="J230" s="2">
+        <v>-53610.46</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C231" s="2">
+        <v>-92097.044999999998</v>
+      </c>
+      <c r="D231" s="2">
+        <v>-53550.097000000002</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I231" s="2">
+        <v>-92135.84</v>
+      </c>
+      <c r="J231" s="2">
+        <v>-53599.94</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="A232" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C232" s="2">
+        <v>-92090.922000000006</v>
+      </c>
+      <c r="D232" s="2">
+        <v>-53511.038999999997</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I232" s="2">
+        <v>-92128.65</v>
+      </c>
+      <c r="J232" s="2">
+        <v>-53597.2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="A233" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C233" s="2">
+        <v>-92089.116999999998</v>
+      </c>
+      <c r="D233" s="2">
+        <v>-53499.207999999999</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I233" s="2">
+        <v>-92125.869000000006</v>
+      </c>
+      <c r="J233" s="2">
+        <v>-53572.309000000001</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C234" s="2">
+        <v>-92100.332999999999</v>
+      </c>
+      <c r="D234" s="2">
+        <v>-53499.578999999998</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I234" s="2">
+        <v>-92127.839000000007</v>
+      </c>
+      <c r="J234" s="2">
+        <v>-53566.978999999999</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C235" s="2">
+        <v>-92094.826000000001</v>
+      </c>
+      <c r="D235" s="2">
+        <v>-53444.478000000003</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I235" s="2">
+        <v>-92125.597999999998</v>
+      </c>
+      <c r="J235" s="2">
+        <v>-53533.169000000002</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C236" s="2">
+        <v>-92088.936000000002</v>
+      </c>
+      <c r="D236" s="2">
+        <v>-53444.247000000003</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I236" s="2">
+        <v>-92123.627999999997</v>
+      </c>
+      <c r="J236" s="2">
+        <v>-53503.387999999999</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="A237" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C237" s="2">
+        <v>-92085.656000000003</v>
+      </c>
+      <c r="D237" s="2">
+        <v>-53407.112999999998</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I237" s="2">
+        <v>-92128.808000000005</v>
+      </c>
+      <c r="J237" s="2">
+        <v>-53501.447999999997</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="A238" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C238" s="2">
+        <v>-92085.705000000002</v>
+      </c>
+      <c r="D238" s="2">
+        <v>-53396.345999999998</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I238" s="2">
+        <v>-92145.027000000002</v>
+      </c>
+      <c r="J238" s="2">
+        <v>-53501.487999999998</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="A239" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C239" s="2">
+        <v>-92082.425000000003</v>
+      </c>
+      <c r="D239" s="2">
+        <v>-53372.106</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I239" s="2">
+        <v>-92145.467000000004</v>
+      </c>
+      <c r="J239" s="2">
+        <v>-53500.658000000003</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="A240" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C240" s="2">
+        <v>-92075.623000000007</v>
+      </c>
+      <c r="D240" s="2">
+        <v>-53295.925000000003</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I240" s="2">
+        <v>-92117.956000000006</v>
+      </c>
+      <c r="J240" s="2">
+        <v>-53445.207000000002</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C241" s="2">
+        <v>-92070.260999999999</v>
+      </c>
+      <c r="D241" s="2">
+        <v>-53233.404000000002</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I241" s="2">
+        <v>-92116.732999999993</v>
+      </c>
+      <c r="J241" s="2">
+        <v>-53437.692999999999</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C242" s="2">
+        <v>-92065.38</v>
+      </c>
+      <c r="D242" s="2">
+        <v>-53178.832999999999</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I242" s="2">
+        <v>-92110.574999999997</v>
+      </c>
+      <c r="J242" s="2">
+        <v>-53395.027000000002</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C243" s="2">
+        <v>-92060.289000000004</v>
+      </c>
+      <c r="D243" s="2">
+        <v>-53124.531999999999</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I243" s="2">
+        <v>-92106.434999999998</v>
+      </c>
+      <c r="J243" s="2">
+        <v>-53377.845999999998</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C244" s="2">
+        <v>-92053.937999999995</v>
+      </c>
+      <c r="D244" s="2">
+        <v>-53057.080999999998</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I244" s="2">
+        <v>-92099.603000000003</v>
+      </c>
+      <c r="J244" s="2">
+        <v>-53300.964999999997</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="A245" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C245" s="2">
+        <v>-92052.028000000006</v>
+      </c>
+      <c r="D245" s="2">
+        <v>-53039.000999999997</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I245" s="2">
+        <v>-92096.713000000003</v>
+      </c>
+      <c r="J245" s="2">
+        <v>-53276.904999999999</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="A246" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I246" s="2">
+        <v>-92088.611000000004</v>
+      </c>
+      <c r="J246" s="2">
+        <v>-53195.803</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10">
+      <c r="A247" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I247" s="2">
+        <v>-92082.188999999998</v>
+      </c>
+      <c r="J247" s="2">
+        <v>-53133.442000000003</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="A248" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I248" s="2">
+        <v>-92075.017999999996</v>
+      </c>
+      <c r="J248" s="2">
+        <v>-53059.491999999998</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="A249" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I249" s="2">
+        <v>-92078.857999999993</v>
+      </c>
+      <c r="J249" s="2">
+        <v>-53054.542000000001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="A250" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I250" s="2">
+        <v>-92075.248000000007</v>
+      </c>
+      <c r="J250" s="2">
+        <v>-53036.642</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="A251" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I251" s="2">
+        <v>-92072.508000000002</v>
+      </c>
+      <c r="J251" s="2">
+        <v>-53035.321000000004</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C253" s="2">
+        <v>-92045.226999999999</v>
+      </c>
+      <c r="D253" s="2">
+        <v>-52969.741000000002</v>
+      </c>
+      <c r="H253" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I253" s="2">
+        <v>-92069.876999999993</v>
+      </c>
+      <c r="J253" s="2">
+        <v>-53012.050999999999</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254" s="2">
+        <v>-92040.096000000005</v>
+      </c>
+      <c r="D254" s="2">
+        <v>-52919.360000000001</v>
+      </c>
+      <c r="H254" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I254" s="2">
+        <v>-92063.486000000004</v>
+      </c>
+      <c r="J254" s="2">
+        <v>-52943.370999999999</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C255" s="2">
+        <v>-92033.255000000005</v>
+      </c>
+      <c r="D255" s="2">
+        <v>-52852.959999999999</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I255" s="2">
+        <v>-92057.255999999994</v>
+      </c>
+      <c r="J255" s="2">
+        <v>-52883.69</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C256" s="2">
+        <v>-92024.144</v>
+      </c>
+      <c r="D256" s="2">
+        <v>-52760.949000000001</v>
+      </c>
+      <c r="H256" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I256" s="2">
+        <v>-92052.455000000002</v>
+      </c>
+      <c r="J256" s="2">
+        <v>-52837.68</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C257" s="2">
+        <v>-92015.831999999995</v>
+      </c>
+      <c r="D257" s="2">
+        <v>-52679.078000000001</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I257" s="2">
+        <v>-92045.254000000001</v>
+      </c>
+      <c r="J257" s="2">
+        <v>-52765.548999999999</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C258" s="2">
+        <v>-92008.270999999993</v>
+      </c>
+      <c r="D258" s="2">
+        <v>-52603.546999999999</v>
+      </c>
+      <c r="H258" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I258" s="2">
+        <v>-92039.142999999996</v>
+      </c>
+      <c r="J258" s="2">
+        <v>-52702.417999999998</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="A259" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C259" s="2">
+        <v>-92002.81</v>
+      </c>
+      <c r="D259" s="2">
+        <v>-52548.817000000003</v>
+      </c>
+      <c r="H259" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I259" s="2">
+        <v>-92034.792000000001</v>
+      </c>
+      <c r="J259" s="2">
+        <v>-52657.508000000002</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="A260" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C260" s="2">
+        <v>-91997.57</v>
+      </c>
+      <c r="D260" s="2">
+        <v>-52496.266000000003</v>
+      </c>
+      <c r="H260" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I260" s="2">
+        <v>-92024.941000000006</v>
+      </c>
+      <c r="J260" s="2">
+        <v>-52562.326999999997</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C261" s="2">
+        <v>-91995.778999999995</v>
+      </c>
+      <c r="D261" s="2">
+        <v>-52478.175999999999</v>
+      </c>
+      <c r="H261" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I261" s="2">
+        <v>-92020.800000000003</v>
+      </c>
+      <c r="J261" s="2">
+        <v>-52519.067000000003</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C262" s="2">
+        <v>-91993.209000000003</v>
+      </c>
+      <c r="D262" s="2">
+        <v>-52452.055999999997</v>
+      </c>
+      <c r="H262" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I262" s="2">
+        <v>-92018.35</v>
+      </c>
+      <c r="J262" s="2">
+        <v>-52494.156000000003</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="A263" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C263" s="2">
+        <v>-91986.23</v>
+      </c>
+      <c r="D263" s="2">
+        <v>-52380.906000000003</v>
+      </c>
+      <c r="H263" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I263" s="6">
+        <v>-92023.24</v>
+      </c>
+      <c r="J263" s="6">
+        <v>-52475.385999999999</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="A264" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C264" s="2">
+        <v>-91981.349000000002</v>
+      </c>
+      <c r="D264" s="2">
+        <v>-52331.144</v>
+      </c>
+      <c r="H264" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I264" s="2">
+        <v>-92015.798999999999</v>
+      </c>
+      <c r="J264" s="2">
+        <v>-52470.915999999997</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="A265" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C265" s="2">
+        <v>-91975.902000000002</v>
+      </c>
+      <c r="D265" s="2">
+        <v>-52275.603000000003</v>
+      </c>
+      <c r="H265" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I265" s="2">
+        <v>-92013.718999999997</v>
+      </c>
+      <c r="J265" s="2">
+        <v>-52450.016000000003</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C266" s="2">
+        <v>-91974.172999999995</v>
+      </c>
+      <c r="D266" s="2">
+        <v>-52251.925999999999</v>
+      </c>
+      <c r="H266" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I266" s="2">
+        <v>-92006.608999999997</v>
+      </c>
+      <c r="J266" s="2">
+        <v>-52378.864000000001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C267" s="2">
+        <v>-91970.532999999996</v>
+      </c>
+      <c r="D267" s="2">
+        <v>-52233.343000000001</v>
+      </c>
+      <c r="H267" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I267" s="2">
+        <v>-92001.638000000006</v>
+      </c>
+      <c r="J267" s="2">
+        <v>-52329.110999999997</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="A268" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C268" s="2">
+        <v>-91964.752999999997</v>
+      </c>
+      <c r="D268" s="2">
+        <v>-52215.519</v>
+      </c>
+      <c r="H268" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I268" s="2">
+        <v>-91996.09</v>
+      </c>
+      <c r="J268" s="2">
+        <v>-52273.58</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="A269" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C269" s="2">
+        <v>-91956.793999999994</v>
+      </c>
+      <c r="D269" s="2">
+        <v>-52198.555</v>
+      </c>
+      <c r="H269" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I269" s="2">
+        <v>-91988.191999999995</v>
+      </c>
+      <c r="J269" s="2">
+        <v>-52194.546000000002</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="A270" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C270" s="2">
+        <v>-91946.38</v>
+      </c>
+      <c r="D270" s="2">
+        <v>-52183.008000000002</v>
+      </c>
+      <c r="H270" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I270" s="2">
+        <v>-91948.562000000005</v>
+      </c>
+      <c r="J270" s="2">
+        <v>-52155.567999999999</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="A271" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C271" s="2">
+        <v>-91934.104999999996</v>
+      </c>
+      <c r="D271" s="2">
+        <v>-52168.84</v>
+      </c>
+      <c r="H271" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I271" s="2">
+        <v>-91916.910999999993</v>
+      </c>
+      <c r="J271" s="2">
+        <v>-52124.438000000002</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="A272" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C272" s="2">
+        <v>-91920.880999999994</v>
+      </c>
+      <c r="D272" s="2">
+        <v>-52154.726000000002</v>
+      </c>
+      <c r="H272" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I272" s="2">
+        <v>-91912.001000000004</v>
+      </c>
+      <c r="J272" s="2">
+        <v>-52124.036</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="A273" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C273" s="2">
+        <v>-91916.384000000005</v>
+      </c>
+      <c r="D273" s="2">
+        <v>-52145.597999999998</v>
+      </c>
+      <c r="H273" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I273" s="2">
+        <v>-91877.51</v>
+      </c>
+      <c r="J273" s="2">
+        <v>-52090.927000000003</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="A274" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C274" s="2">
+        <v>-91887.104000000007</v>
+      </c>
+      <c r="D274" s="2">
+        <v>-52117.792000000001</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.83203125" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" s="3">
+        <v>-92069.876999999993</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3">
+        <v>-92063.486000000004</v>
+      </c>
+      <c r="C3" s="3">
+        <v>-52943.370999999999</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G3" s="3">
+        <v>-52919.360000000001</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-92057.255999999994</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-52883.69</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G4" s="3">
+        <v>-52852.959999999999</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-92002.81</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-52562.326999999997</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-92020.800000000003</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-52519.067000000003</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-91995.778999999995</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-92018.35</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-52494.156000000003</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-52452.055999999997</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-52470.915999999997</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-92013.718999999997</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-52450.016000000003</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-92006.608999999997</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-92001.638000000006</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-91996.09</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-52273.58</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="3">
+        <v>-91988.191999999995</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-91956.793999999994</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-52155.567999999999</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="3">
+        <v>-91946.38</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="3">
+        <v>-91912.001000000004</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-52124.036</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-91920.880999999994</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="E23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-52117.792000000001</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2">
+        <v>-92169.998999999996</v>
+      </c>
+      <c r="J2">
+        <v>-54024.735999999997</v>
+      </c>
+      <c r="K2">
+        <v>-92146.788</v>
+      </c>
+      <c r="L2">
+        <v>-53996.226000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3">
+        <v>-92166.127999999997</v>
+      </c>
+      <c r="J3">
+        <v>-53984.845000000001</v>
+      </c>
+      <c r="K3">
+        <v>-92141.717000000004</v>
+      </c>
+      <c r="L3">
+        <v>-53943.495000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4">
+        <v>-92161.087</v>
+      </c>
+      <c r="J4">
+        <v>-53933.105000000003</v>
+      </c>
+      <c r="K4">
+        <v>-92136.656000000003</v>
+      </c>
+      <c r="L4">
+        <v>-53890.754000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5">
+        <v>-92155.766000000003</v>
+      </c>
+      <c r="J5">
+        <v>-53878.423999999999</v>
+      </c>
+      <c r="K5">
+        <v>-92131.585000000006</v>
+      </c>
+      <c r="L5">
+        <v>-53838.023000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6">
+        <v>-92153.675000000003</v>
+      </c>
+      <c r="J6">
+        <v>-53856.993000000002</v>
+      </c>
+      <c r="K6">
+        <v>-92126.513999999996</v>
+      </c>
+      <c r="L6">
+        <v>-53785.283000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7">
+        <v>-92148.834000000003</v>
+      </c>
+      <c r="J7">
+        <v>-53807.222999999998</v>
+      </c>
+      <c r="K7">
+        <v>-92128.414000000004</v>
+      </c>
+      <c r="L7">
+        <v>-53785.101999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8">
+        <v>-92146.504000000001</v>
+      </c>
+      <c r="J8">
+        <v>-53783.302000000003</v>
+      </c>
+      <c r="K8">
+        <v>-92119.282000000007</v>
+      </c>
+      <c r="L8">
+        <v>-53725.962</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H9" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9">
+        <v>-92143.993000000002</v>
+      </c>
+      <c r="J9">
+        <v>-53757.451999999997</v>
+      </c>
+      <c r="K9">
+        <v>-92117.262000000002</v>
+      </c>
+      <c r="L9">
+        <v>-53718.271999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10">
+        <v>-92139.152000000002</v>
+      </c>
+      <c r="J10">
+        <v>-53707.680999999997</v>
+      </c>
+      <c r="K10">
+        <v>-92111.691000000006</v>
+      </c>
+      <c r="L10">
+        <v>-53668.580999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11">
+        <v>-92131.199999999997</v>
+      </c>
+      <c r="J11">
+        <v>-53618.68</v>
+      </c>
+      <c r="K11">
+        <v>-92106.37</v>
+      </c>
+      <c r="L11">
+        <v>-53621.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" t="s">
+        <v>161</v>
+      </c>
+      <c r="H12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12">
+        <v>-92142.43</v>
+      </c>
+      <c r="J12">
+        <v>-53617.56</v>
+      </c>
+      <c r="K12">
+        <v>-92104.17</v>
+      </c>
+      <c r="L12">
+        <v>-53603.08</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13">
+        <v>-92139.83</v>
+      </c>
+      <c r="J13">
+        <v>-53610.46</v>
+      </c>
+      <c r="K13">
+        <v>-92099.849000000002</v>
+      </c>
+      <c r="L13">
+        <v>-53567.078999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" t="s">
+        <v>175</v>
+      </c>
+      <c r="I14">
+        <v>-92135.84</v>
+      </c>
+      <c r="J14">
+        <v>-53599.94</v>
+      </c>
+      <c r="K14">
+        <v>-92097.044999999998</v>
+      </c>
+      <c r="L14">
+        <v>-53550.097000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" t="s">
+        <v>180</v>
+      </c>
+      <c r="H15" t="s">
+        <v>181</v>
+      </c>
+      <c r="I15">
+        <v>-92128.65</v>
+      </c>
+      <c r="J15">
+        <v>-53597.2</v>
+      </c>
+      <c r="K15">
+        <v>-92090.922000000006</v>
+      </c>
+      <c r="L15">
+        <v>-53511.038999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16">
+        <v>-92125.869000000006</v>
+      </c>
+      <c r="J16">
+        <v>-53572.309000000001</v>
+      </c>
+      <c r="K16">
+        <v>-92089.116999999998</v>
+      </c>
+      <c r="L16">
+        <v>-53499.207999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17">
+        <v>-92127.839000000007</v>
+      </c>
+      <c r="J17">
+        <v>-53566.978999999999</v>
+      </c>
+      <c r="K17">
+        <v>-92100.332999999999</v>
+      </c>
+      <c r="L17">
+        <v>-53499.578999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18">
+        <v>-92125.597999999998</v>
+      </c>
+      <c r="J18">
+        <v>-53533.169000000002</v>
+      </c>
+      <c r="K18">
+        <v>-92094.826000000001</v>
+      </c>
+      <c r="L18">
+        <v>-53444.478000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" t="s">
+        <v>193</v>
+      </c>
+      <c r="I19">
+        <v>-92123.627999999997</v>
+      </c>
+      <c r="J19">
+        <v>-53503.387999999999</v>
+      </c>
+      <c r="K19">
+        <v>-92088.936000000002</v>
+      </c>
+      <c r="L19">
+        <v>-53444.247000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20">
+        <v>-92128.808000000005</v>
+      </c>
+      <c r="J20">
+        <v>-53501.447999999997</v>
+      </c>
+      <c r="K20">
+        <v>-92085.656000000003</v>
+      </c>
+      <c r="L20">
+        <v>-53407.112999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" t="s">
+        <v>213</v>
+      </c>
+      <c r="G21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21">
+        <v>-92145.027000000002</v>
+      </c>
+      <c r="J21">
+        <v>-53501.487999999998</v>
+      </c>
+      <c r="K21">
+        <v>-92085.705000000002</v>
+      </c>
+      <c r="L21">
+        <v>-53396.345999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" t="s">
+        <v>218</v>
+      </c>
+      <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
+        <v>219</v>
+      </c>
+      <c r="G22" t="s">
+        <v>220</v>
+      </c>
+      <c r="H22" t="s">
+        <v>221</v>
+      </c>
+      <c r="I22">
+        <v>-92145.467000000004</v>
+      </c>
+      <c r="J22">
+        <v>-53500.658000000003</v>
+      </c>
+      <c r="K22">
+        <v>-92082.425000000003</v>
+      </c>
+      <c r="L22">
+        <v>-53372.106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>222</v>
+      </c>
+      <c r="C23" t="s">
+        <v>223</v>
+      </c>
+      <c r="D23" t="s">
+        <v>224</v>
+      </c>
+      <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" t="s">
+        <v>225</v>
+      </c>
+      <c r="G23" t="s">
+        <v>226</v>
+      </c>
+      <c r="H23" t="s">
+        <v>227</v>
+      </c>
+      <c r="I23">
+        <v>-92117.956000000006</v>
+      </c>
+      <c r="J23">
+        <v>-53445.207000000002</v>
+      </c>
+      <c r="K23">
+        <v>-92075.623000000007</v>
+      </c>
+      <c r="L23">
+        <v>-53295.925000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" t="s">
+        <v>231</v>
+      </c>
+      <c r="G24" t="s">
+        <v>232</v>
+      </c>
+      <c r="H24" t="s">
+        <v>233</v>
+      </c>
+      <c r="I24">
+        <v>-92116.732999999993</v>
+      </c>
+      <c r="J24">
+        <v>-53437.692999999999</v>
+      </c>
+      <c r="K24">
+        <v>-92070.260999999999</v>
+      </c>
+      <c r="L24">
+        <v>-53233.404000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" t="s">
+        <v>236</v>
+      </c>
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" t="s">
+        <v>238</v>
+      </c>
+      <c r="G25" t="s">
+        <v>239</v>
+      </c>
+      <c r="H25" t="s">
+        <v>240</v>
+      </c>
+      <c r="I25">
+        <v>-92110.574999999997</v>
+      </c>
+      <c r="J25">
+        <v>-53395.027000000002</v>
+      </c>
+      <c r="K25">
+        <v>-92065.38</v>
+      </c>
+      <c r="L25">
+        <v>-53178.832999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" t="s">
+        <v>243</v>
+      </c>
+      <c r="D26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
+        <v>245</v>
+      </c>
+      <c r="G26" t="s">
+        <v>246</v>
+      </c>
+      <c r="H26" t="s">
+        <v>247</v>
+      </c>
+      <c r="I26">
+        <v>-92106.434999999998</v>
+      </c>
+      <c r="J26">
+        <v>-53377.845999999998</v>
+      </c>
+      <c r="K26">
+        <v>-92060.289000000004</v>
+      </c>
+      <c r="L26">
+        <v>-53124.531999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D27" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27" t="s">
+        <v>253</v>
+      </c>
+      <c r="H27" t="s">
+        <v>254</v>
+      </c>
+      <c r="I27">
+        <v>-92099.603000000003</v>
+      </c>
+      <c r="J27">
+        <v>-53300.964999999997</v>
+      </c>
+      <c r="K27">
+        <v>-92053.937999999995</v>
+      </c>
+      <c r="L27">
+        <v>-53057.080999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B28" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" t="s">
+        <v>257</v>
+      </c>
+      <c r="D28" t="s">
+        <v>258</v>
+      </c>
+      <c r="E28" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" t="s">
+        <v>259</v>
+      </c>
+      <c r="G28" t="s">
+        <v>260</v>
+      </c>
+      <c r="H28" t="s">
+        <v>261</v>
+      </c>
+      <c r="I28">
+        <v>-92096.713000000003</v>
+      </c>
+      <c r="J28">
+        <v>-53276.904999999999</v>
+      </c>
+      <c r="K28">
+        <v>-92052.028000000006</v>
+      </c>
+      <c r="L28">
+        <v>-53039.000999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B29" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" t="s">
+        <v>265</v>
+      </c>
+      <c r="I29">
+        <v>-92088.611000000004</v>
+      </c>
+      <c r="J29">
+        <v>-53195.803</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" t="s">
+        <v>268</v>
+      </c>
+      <c r="D30" t="s">
+        <v>269</v>
+      </c>
+      <c r="I30">
+        <v>-92082.188999999998</v>
+      </c>
+      <c r="J30">
+        <v>-53133.442000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B31" t="s">
+        <v>271</v>
+      </c>
+      <c r="C31" t="s">
+        <v>272</v>
+      </c>
+      <c r="D31" t="s">
+        <v>273</v>
+      </c>
+      <c r="I31">
+        <v>-92075.017999999996</v>
+      </c>
+      <c r="J31">
+        <v>-53059.491999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>274</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" t="s">
+        <v>276</v>
+      </c>
+      <c r="D32" t="s">
+        <v>277</v>
+      </c>
+      <c r="I32">
+        <v>-92078.857999999993</v>
+      </c>
+      <c r="J32">
+        <v>-53054.542000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>278</v>
+      </c>
+      <c r="B33" t="s">
+        <v>279</v>
+      </c>
+      <c r="C33" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" t="s">
+        <v>281</v>
+      </c>
+      <c r="I33">
+        <v>-92075.248000000007</v>
+      </c>
+      <c r="J33">
+        <v>-53036.642</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>282</v>
+      </c>
+      <c r="B34" t="s">
+        <v>283</v>
+      </c>
+      <c r="C34" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" t="s">
+        <v>285</v>
+      </c>
+      <c r="I34">
+        <v>-92072.508000000002</v>
+      </c>
+      <c r="J34">
+        <v>-53035.321000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>